--- a/SunCount_data.xlsx
+++ b/SunCount_data.xlsx
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'buyback_by_category'!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'buyback_prices'!$A$1:$K$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'buyback_prices'!$A$1:$K$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'capex_components'!$A$1:$J$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'capex_estimate'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'equipment_offers'!$A$1:$Q$10</definedName>
@@ -1056,31 +1056,31 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>19854</v>
+        <v>19773</v>
       </c>
       <c r="G2" t="n">
         <v>6181</v>
       </c>
       <c r="H2" t="n">
-        <v>13673</v>
+        <v>13592</v>
       </c>
       <c r="I2" t="n">
-        <v>68.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="J2" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="K2" t="n">
         <v>10.1</v>
       </c>
       <c r="L2" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="M2" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="N2" t="n">
-        <v>22587</v>
+        <v>21448</v>
       </c>
     </row>
     <row r="3">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>30087</v>
+        <v>29952</v>
       </c>
       <c r="G3" t="n">
         <v>6940</v>
       </c>
       <c r="H3" t="n">
-        <v>23148</v>
+        <v>23012</v>
       </c>
       <c r="I3" t="n">
-        <v>76.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="J3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="L3" t="n">
         <v>12.5</v>
@@ -1126,7 +1126,7 @@
         <v>10.6</v>
       </c>
       <c r="N3" t="n">
-        <v>170369</v>
+        <v>168441</v>
       </c>
     </row>
     <row r="4">
@@ -1148,25 +1148,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>18009</v>
+        <v>17929</v>
       </c>
       <c r="G4" t="n">
         <v>4336</v>
       </c>
       <c r="H4" t="n">
-        <v>13673</v>
+        <v>13592</v>
       </c>
       <c r="I4" t="n">
-        <v>75.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="J4" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="K4" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="L4" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>-10018</v>
+        <v>-11157</v>
       </c>
     </row>
     <row r="5">
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>28012</v>
+        <v>27876</v>
       </c>
       <c r="G5" t="n">
         <v>4864</v>
       </c>
       <c r="H5" t="n">
-        <v>23148</v>
+        <v>23012</v>
       </c>
       <c r="I5" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="J5" t="n">
         <v>8.9</v>
       </c>
       <c r="K5" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="L5" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="M5" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="N5" t="n">
-        <v>133688</v>
+        <v>131760</v>
       </c>
     </row>
     <row r="6">
@@ -1242,19 +1242,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>21237</v>
+        <v>21166</v>
       </c>
       <c r="G6" t="n">
         <v>9273</v>
       </c>
       <c r="H6" t="n">
-        <v>11964</v>
+        <v>11893</v>
       </c>
       <c r="I6" t="n">
-        <v>56.3</v>
+        <v>56.2</v>
       </c>
       <c r="J6" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="K6" t="n">
         <v>9.4</v>
@@ -1266,7 +1266,7 @@
         <v>18.9</v>
       </c>
       <c r="N6" t="n">
-        <v>53008</v>
+        <v>52011</v>
       </c>
     </row>
     <row r="7">
@@ -1288,31 +1288,31 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>30666</v>
+        <v>30547</v>
       </c>
       <c r="G7" t="n">
         <v>10411</v>
       </c>
       <c r="H7" t="n">
-        <v>20254</v>
+        <v>20135</v>
       </c>
       <c r="I7" t="n">
-        <v>66</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>6.5</v>
       </c>
       <c r="L7" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="M7" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="N7" t="n">
-        <v>190703</v>
+        <v>189015</v>
       </c>
     </row>
     <row r="8">
@@ -1334,31 +1334,31 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>18469</v>
+        <v>18399</v>
       </c>
       <c r="G8" t="n">
         <v>6506</v>
       </c>
       <c r="H8" t="n">
-        <v>11964</v>
+        <v>11893</v>
       </c>
       <c r="I8" t="n">
-        <v>64.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J8" t="n">
         <v>13.5</v>
       </c>
       <c r="K8" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="L8" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="M8" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="N8" t="n">
-        <v>4091</v>
+        <v>3094</v>
       </c>
     </row>
     <row r="9">
@@ -1380,31 +1380,31 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>27552</v>
+        <v>27433</v>
       </c>
       <c r="G9" t="n">
         <v>7298</v>
       </c>
       <c r="H9" t="n">
-        <v>20254</v>
+        <v>20135</v>
       </c>
       <c r="I9" t="n">
-        <v>73.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="K9" t="n">
         <v>7.3</v>
       </c>
       <c r="L9" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="M9" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="N9" t="n">
-        <v>135671</v>
+        <v>133983</v>
       </c>
     </row>
     <row r="10">
@@ -1426,31 +1426,31 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>22620</v>
+        <v>22560</v>
       </c>
       <c r="G10" t="n">
         <v>12366</v>
       </c>
       <c r="H10" t="n">
-        <v>10254</v>
+        <v>10194</v>
       </c>
       <c r="I10" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="J10" t="n">
         <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="L10" t="n">
         <v>16.6</v>
       </c>
       <c r="M10" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="N10" t="n">
-        <v>83434</v>
+        <v>82579</v>
       </c>
     </row>
     <row r="11">
@@ -1472,16 +1472,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>31244</v>
+        <v>31142</v>
       </c>
       <c r="G11" t="n">
         <v>13884</v>
       </c>
       <c r="H11" t="n">
-        <v>17360</v>
+        <v>17258</v>
       </c>
       <c r="I11" t="n">
-        <v>55.6</v>
+        <v>55.4</v>
       </c>
       <c r="J11" t="n">
         <v>8</v>
@@ -1496,7 +1496,7 @@
         <v>9.6</v>
       </c>
       <c r="N11" t="n">
-        <v>211037</v>
+        <v>209591</v>
       </c>
     </row>
     <row r="12">
@@ -1518,16 +1518,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18930</v>
+        <v>18869</v>
       </c>
       <c r="G12" t="n">
         <v>8676</v>
       </c>
       <c r="H12" t="n">
-        <v>10254</v>
+        <v>10194</v>
       </c>
       <c r="I12" t="n">
-        <v>54.2</v>
+        <v>54</v>
       </c>
       <c r="J12" t="n">
         <v>13.2</v>
@@ -1536,13 +1536,13 @@
         <v>10.6</v>
       </c>
       <c r="L12" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="M12" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="N12" t="n">
-        <v>18201</v>
+        <v>17347</v>
       </c>
     </row>
     <row r="13">
@@ -1564,16 +1564,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>27092</v>
+        <v>26990</v>
       </c>
       <c r="G13" t="n">
         <v>9732</v>
       </c>
       <c r="H13" t="n">
-        <v>17360</v>
+        <v>17258</v>
       </c>
       <c r="I13" t="n">
-        <v>64.09999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="J13" t="n">
         <v>9.199999999999999</v>
@@ -1582,13 +1582,13 @@
         <v>7.4</v>
       </c>
       <c r="L13" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="M13" t="n">
         <v>13.7</v>
       </c>
       <c r="N13" t="n">
-        <v>137651</v>
+        <v>136204</v>
       </c>
     </row>
     <row r="14">
@@ -1610,31 +1610,31 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>24001</v>
+        <v>23951</v>
       </c>
       <c r="G14" t="n">
         <v>15456</v>
       </c>
       <c r="H14" t="n">
-        <v>8545</v>
+        <v>8495</v>
       </c>
       <c r="I14" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J14" t="n">
         <v>10.4</v>
       </c>
       <c r="K14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="L14" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="M14" t="n">
         <v>14.9</v>
       </c>
       <c r="N14" t="n">
-        <v>113809</v>
+        <v>113097</v>
       </c>
     </row>
     <row r="15">
@@ -1656,16 +1656,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>31819</v>
+        <v>31735</v>
       </c>
       <c r="G15" t="n">
         <v>17353</v>
       </c>
       <c r="H15" t="n">
-        <v>14467</v>
+        <v>14382</v>
       </c>
       <c r="I15" t="n">
-        <v>45.5</v>
+        <v>45.3</v>
       </c>
       <c r="J15" t="n">
         <v>7.8</v>
@@ -1677,10 +1677,10 @@
         <v>11.8</v>
       </c>
       <c r="M15" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>231320</v>
+        <v>230115</v>
       </c>
     </row>
     <row r="16">
@@ -1702,31 +1702,31 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>19388</v>
+        <v>19338</v>
       </c>
       <c r="G16" t="n">
         <v>10843</v>
       </c>
       <c r="H16" t="n">
-        <v>8545</v>
+        <v>8495</v>
       </c>
       <c r="I16" t="n">
-        <v>44.1</v>
+        <v>43.9</v>
       </c>
       <c r="J16" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="K16" t="n">
         <v>10.3</v>
       </c>
       <c r="L16" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="M16" t="n">
         <v>20.9</v>
       </c>
       <c r="N16" t="n">
-        <v>32278</v>
+        <v>31567</v>
       </c>
     </row>
     <row r="17">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>26630</v>
+        <v>26545</v>
       </c>
       <c r="G17" t="n">
         <v>12164</v>
       </c>
       <c r="H17" t="n">
-        <v>14467</v>
+        <v>14382</v>
       </c>
       <c r="I17" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="J17" t="n">
         <v>9.4</v>
@@ -1769,10 +1769,10 @@
         <v>14.1</v>
       </c>
       <c r="M17" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="N17" t="n">
-        <v>139598</v>
+        <v>138393</v>
       </c>
     </row>
     <row r="18">
@@ -1794,16 +1794,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>25384</v>
+        <v>25344</v>
       </c>
       <c r="G18" t="n">
         <v>18547</v>
       </c>
       <c r="H18" t="n">
-        <v>6837</v>
+        <v>6797</v>
       </c>
       <c r="I18" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="J18" t="n">
         <v>9.800000000000001</v>
@@ -1818,7 +1818,7 @@
         <v>13.5</v>
       </c>
       <c r="N18" t="n">
-        <v>144227</v>
+        <v>143657</v>
       </c>
     </row>
     <row r="19">
@@ -1840,16 +1840,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>32398</v>
+        <v>32330</v>
       </c>
       <c r="G19" t="n">
         <v>20824</v>
       </c>
       <c r="H19" t="n">
-        <v>11575</v>
+        <v>11507</v>
       </c>
       <c r="I19" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J19" t="n">
         <v>7.7</v>
@@ -1861,10 +1861,10 @@
         <v>11.6</v>
       </c>
       <c r="M19" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>251657</v>
+        <v>250692</v>
       </c>
     </row>
     <row r="20">
@@ -1886,19 +1886,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>19849</v>
+        <v>19809</v>
       </c>
       <c r="G20" t="n">
         <v>13012</v>
       </c>
       <c r="H20" t="n">
-        <v>6837</v>
+        <v>6797</v>
       </c>
       <c r="I20" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="J20" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="K20" t="n">
         <v>10.1</v>
@@ -1910,7 +1910,7 @@
         <v>19.5</v>
       </c>
       <c r="N20" t="n">
-        <v>46389</v>
+        <v>45819</v>
       </c>
     </row>
     <row r="21">
@@ -1932,31 +1932,31 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>26171</v>
+        <v>26103</v>
       </c>
       <c r="G21" t="n">
         <v>14597</v>
       </c>
       <c r="H21" t="n">
-        <v>11575</v>
+        <v>11507</v>
       </c>
       <c r="I21" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="J21" t="n">
         <v>9.5</v>
       </c>
       <c r="K21" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="L21" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="M21" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="N21" t="n">
-        <v>141589</v>
+        <v>140625</v>
       </c>
     </row>
     <row r="22">
@@ -1978,16 +1978,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>26766</v>
+        <v>26736</v>
       </c>
       <c r="G22" t="n">
         <v>21639</v>
       </c>
       <c r="H22" t="n">
-        <v>5127</v>
+        <v>5097</v>
       </c>
       <c r="I22" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="J22" t="n">
         <v>9.300000000000001</v>
@@ -2002,7 +2002,7 @@
         <v>10.6</v>
       </c>
       <c r="N22" t="n">
-        <v>174633</v>
+        <v>174206</v>
       </c>
     </row>
     <row r="23">
@@ -2024,16 +2024,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>32975</v>
+        <v>32924</v>
       </c>
       <c r="G23" t="n">
         <v>24295</v>
       </c>
       <c r="H23" t="n">
-        <v>8680</v>
+        <v>8629</v>
       </c>
       <c r="I23" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="J23" t="n">
         <v>7.6</v>
@@ -2048,7 +2048,7 @@
         <v>8.4</v>
       </c>
       <c r="N23" t="n">
-        <v>271967</v>
+        <v>271244</v>
       </c>
     </row>
     <row r="24">
@@ -2070,22 +2070,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>20308</v>
+        <v>20278</v>
       </c>
       <c r="G24" t="n">
         <v>15181</v>
       </c>
       <c r="H24" t="n">
-        <v>5127</v>
+        <v>5097</v>
       </c>
       <c r="I24" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="J24" t="n">
         <v>12.3</v>
       </c>
       <c r="K24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="L24" t="n">
         <v>18.5</v>
@@ -2094,7 +2094,7 @@
         <v>18.3</v>
       </c>
       <c r="N24" t="n">
-        <v>60484</v>
+        <v>60057</v>
       </c>
     </row>
     <row r="25">
@@ -2116,16 +2116,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>25710</v>
+        <v>25659</v>
       </c>
       <c r="G25" t="n">
         <v>17030</v>
       </c>
       <c r="H25" t="n">
-        <v>8680</v>
+        <v>8629</v>
       </c>
       <c r="I25" t="n">
-        <v>33.8</v>
+        <v>33.6</v>
       </c>
       <c r="J25" t="n">
         <v>9.699999999999999</v>
@@ -2140,7 +2140,7 @@
         <v>13.5</v>
       </c>
       <c r="N25" t="n">
-        <v>143549</v>
+        <v>142826</v>
       </c>
     </row>
     <row r="26">
@@ -2162,13 +2162,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>28093</v>
+        <v>28074</v>
       </c>
       <c r="G26" t="n">
         <v>24606</v>
       </c>
       <c r="H26" t="n">
-        <v>3487</v>
+        <v>3468</v>
       </c>
       <c r="I26" t="n">
         <v>12.4</v>
@@ -2180,13 +2180,13 @@
         <v>7.1</v>
       </c>
       <c r="L26" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="M26" t="n">
         <v>9.9</v>
       </c>
       <c r="N26" t="n">
-        <v>203823</v>
+        <v>203544</v>
       </c>
     </row>
     <row r="27">
@@ -2208,16 +2208,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>33530</v>
+        <v>33497</v>
       </c>
       <c r="G27" t="n">
         <v>27626</v>
       </c>
       <c r="H27" t="n">
-        <v>5904</v>
+        <v>5871</v>
       </c>
       <c r="I27" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="J27" t="n">
         <v>7.4</v>
@@ -2232,7 +2232,7 @@
         <v>8.1</v>
       </c>
       <c r="N27" t="n">
-        <v>291481</v>
+        <v>291009</v>
       </c>
     </row>
     <row r="28">
@@ -2254,16 +2254,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>20750</v>
+        <v>20730</v>
       </c>
       <c r="G28" t="n">
         <v>17263</v>
       </c>
       <c r="H28" t="n">
-        <v>3487</v>
+        <v>3468</v>
       </c>
       <c r="I28" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="J28" t="n">
         <v>12</v>
@@ -2278,7 +2278,7 @@
         <v>17.3</v>
       </c>
       <c r="N28" t="n">
-        <v>74024</v>
+        <v>73745</v>
       </c>
     </row>
     <row r="29">
@@ -2300,16 +2300,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>25269</v>
+        <v>25236</v>
       </c>
       <c r="G29" t="n">
         <v>19365</v>
       </c>
       <c r="H29" t="n">
-        <v>5904</v>
+        <v>5871</v>
       </c>
       <c r="I29" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="J29" t="n">
         <v>9.9</v>
@@ -2318,13 +2318,13 @@
         <v>7.9</v>
       </c>
       <c r="L29" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="M29" t="n">
         <v>13.4</v>
       </c>
       <c r="N29" t="n">
-        <v>145458</v>
+        <v>144986</v>
       </c>
     </row>
     <row r="30">
@@ -2346,19 +2346,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>33093</v>
+        <v>32959</v>
       </c>
       <c r="G30" t="n">
         <v>10305</v>
       </c>
       <c r="H30" t="n">
-        <v>22787</v>
+        <v>22653</v>
       </c>
       <c r="I30" t="n">
-        <v>68.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="J30" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="K30" t="n">
         <v>8.300000000000001</v>
@@ -2367,10 +2367,10 @@
         <v>15.9</v>
       </c>
       <c r="M30" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N30" t="n">
-        <v>73730</v>
+        <v>71831</v>
       </c>
     </row>
     <row r="31">
@@ -2392,19 +2392,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>50149</v>
+        <v>49923</v>
       </c>
       <c r="G31" t="n">
         <v>11570</v>
       </c>
       <c r="H31" t="n">
-        <v>38579</v>
+        <v>38352</v>
       </c>
       <c r="I31" t="n">
-        <v>76.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="J31" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="K31" t="n">
         <v>5.5</v>
@@ -2416,7 +2416,7 @@
         <v>10.2</v>
       </c>
       <c r="N31" t="n">
-        <v>320037</v>
+        <v>316822</v>
       </c>
     </row>
     <row r="32">
@@ -2438,31 +2438,31 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>30017</v>
+        <v>29883</v>
       </c>
       <c r="G32" t="n">
         <v>7230</v>
       </c>
       <c r="H32" t="n">
-        <v>22787</v>
+        <v>22653</v>
       </c>
       <c r="I32" t="n">
-        <v>75.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="J32" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="K32" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="M32" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="N32" t="n">
-        <v>19369</v>
+        <v>17470</v>
       </c>
     </row>
     <row r="33">
@@ -2484,31 +2484,31 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>46689</v>
+        <v>46463</v>
       </c>
       <c r="G33" t="n">
         <v>8110</v>
       </c>
       <c r="H33" t="n">
-        <v>38579</v>
+        <v>38352</v>
       </c>
       <c r="I33" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="J33" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K33" t="n">
         <v>5.9</v>
       </c>
       <c r="L33" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="M33" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="N33" t="n">
-        <v>258881</v>
+        <v>255666</v>
       </c>
     </row>
     <row r="34">
@@ -2530,16 +2530,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>35395</v>
+        <v>35278</v>
       </c>
       <c r="G34" t="n">
         <v>15456</v>
       </c>
       <c r="H34" t="n">
-        <v>19939</v>
+        <v>19822</v>
       </c>
       <c r="I34" t="n">
-        <v>56.3</v>
+        <v>56.2</v>
       </c>
       <c r="J34" t="n">
         <v>11.4</v>
@@ -2548,13 +2548,13 @@
         <v>7.8</v>
       </c>
       <c r="L34" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="M34" t="n">
         <v>16.8</v>
       </c>
       <c r="N34" t="n">
-        <v>124380</v>
+        <v>122719</v>
       </c>
     </row>
     <row r="35">
@@ -2576,16 +2576,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>51110</v>
+        <v>50912</v>
       </c>
       <c r="G35" t="n">
         <v>17353</v>
       </c>
       <c r="H35" t="n">
-        <v>33757</v>
+        <v>33559</v>
       </c>
       <c r="I35" t="n">
-        <v>66</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="J35" t="n">
         <v>7.9</v>
@@ -2600,7 +2600,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>353872</v>
+        <v>351059</v>
       </c>
     </row>
     <row r="36">
@@ -2622,31 +2622,31 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>30782</v>
+        <v>30665</v>
       </c>
       <c r="G36" t="n">
         <v>10843</v>
       </c>
       <c r="H36" t="n">
-        <v>19939</v>
+        <v>19822</v>
       </c>
       <c r="I36" t="n">
-        <v>64.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>13.1</v>
       </c>
       <c r="K36" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="L36" t="n">
         <v>17.1</v>
       </c>
       <c r="M36" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="N36" t="n">
-        <v>42850</v>
+        <v>41189</v>
       </c>
     </row>
     <row r="37">
@@ -2668,16 +2668,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>45921</v>
+        <v>45723</v>
       </c>
       <c r="G37" t="n">
         <v>12164</v>
       </c>
       <c r="H37" t="n">
-        <v>33757</v>
+        <v>33559</v>
       </c>
       <c r="I37" t="n">
-        <v>73.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J37" t="n">
         <v>8.800000000000001</v>
@@ -2686,13 +2686,13 @@
         <v>6</v>
       </c>
       <c r="L37" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="M37" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="N37" t="n">
-        <v>262150</v>
+        <v>259337</v>
       </c>
     </row>
     <row r="38">
@@ -2714,16 +2714,16 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>37700</v>
+        <v>37599</v>
       </c>
       <c r="G38" t="n">
         <v>20609</v>
       </c>
       <c r="H38" t="n">
-        <v>17091</v>
+        <v>16990</v>
       </c>
       <c r="I38" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="J38" t="n">
         <v>10.7</v>
@@ -2732,13 +2732,13 @@
         <v>7.3</v>
       </c>
       <c r="L38" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="M38" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="N38" t="n">
-        <v>175070</v>
+        <v>173646</v>
       </c>
     </row>
     <row r="39">
@@ -2760,16 +2760,16 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>52073</v>
+        <v>51903</v>
       </c>
       <c r="G39" t="n">
         <v>23138</v>
       </c>
       <c r="H39" t="n">
-        <v>28935</v>
+        <v>28765</v>
       </c>
       <c r="I39" t="n">
-        <v>55.6</v>
+        <v>55.4</v>
       </c>
       <c r="J39" t="n">
         <v>7.7</v>
@@ -2784,7 +2784,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>387748</v>
+        <v>385337</v>
       </c>
     </row>
     <row r="40">
@@ -2806,31 +2806,31 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>31549</v>
+        <v>31449</v>
       </c>
       <c r="G40" t="n">
         <v>14458</v>
       </c>
       <c r="H40" t="n">
-        <v>17091</v>
+        <v>16990</v>
       </c>
       <c r="I40" t="n">
-        <v>54.2</v>
+        <v>54</v>
       </c>
       <c r="J40" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="K40" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="M40" t="n">
         <v>19.8</v>
       </c>
       <c r="N40" t="n">
-        <v>66357</v>
+        <v>64933</v>
       </c>
     </row>
     <row r="41">
@@ -2852,16 +2852,16 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>45154</v>
+        <v>44984</v>
       </c>
       <c r="G41" t="n">
         <v>16219</v>
       </c>
       <c r="H41" t="n">
-        <v>28935</v>
+        <v>28765</v>
       </c>
       <c r="I41" t="n">
-        <v>64.09999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="J41" t="n">
         <v>8.9</v>
@@ -2870,13 +2870,13 @@
         <v>6.1</v>
       </c>
       <c r="L41" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="M41" t="n">
         <v>12.3</v>
       </c>
       <c r="N41" t="n">
-        <v>265446</v>
+        <v>263035</v>
       </c>
     </row>
     <row r="42">
@@ -2898,16 +2898,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>39837</v>
+        <v>39756</v>
       </c>
       <c r="G42" t="n">
         <v>25388</v>
       </c>
       <c r="H42" t="n">
-        <v>14449</v>
+        <v>14368</v>
       </c>
       <c r="I42" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="J42" t="n">
         <v>10.1</v>
@@ -2919,10 +2919,10 @@
         <v>13.2</v>
       </c>
       <c r="M42" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="N42" t="n">
-        <v>222086</v>
+        <v>220928</v>
       </c>
     </row>
     <row r="43">
@@ -2944,16 +2944,16 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>52967</v>
+        <v>52829</v>
       </c>
       <c r="G43" t="n">
         <v>28504</v>
       </c>
       <c r="H43" t="n">
-        <v>24463</v>
+        <v>24325</v>
       </c>
       <c r="I43" t="n">
-        <v>46.2</v>
+        <v>46</v>
       </c>
       <c r="J43" t="n">
         <v>7.6</v>
@@ -2968,7 +2968,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>419174</v>
+        <v>417213</v>
       </c>
     </row>
     <row r="44">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>32261</v>
+        <v>32179</v>
       </c>
       <c r="G44" t="n">
         <v>17811</v>
       </c>
       <c r="H44" t="n">
-        <v>14449</v>
+        <v>14368</v>
       </c>
       <c r="I44" t="n">
-        <v>44.8</v>
+        <v>44.6</v>
       </c>
       <c r="J44" t="n">
         <v>12.5</v>
@@ -3011,10 +3011,10 @@
         <v>16.3</v>
       </c>
       <c r="M44" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="N44" t="n">
-        <v>88162</v>
+        <v>87004</v>
       </c>
     </row>
     <row r="45">
@@ -3036,19 +3036,19 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>44443</v>
+        <v>44305</v>
       </c>
       <c r="G45" t="n">
         <v>19980</v>
       </c>
       <c r="H45" t="n">
-        <v>24463</v>
+        <v>24325</v>
       </c>
       <c r="I45" t="n">
-        <v>55</v>
+        <v>54.9</v>
       </c>
       <c r="J45" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="K45" t="n">
         <v>6.2</v>
@@ -3057,10 +3057,10 @@
         <v>11.8</v>
       </c>
       <c r="M45" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="N45" t="n">
-        <v>268509</v>
+        <v>266549</v>
       </c>
     </row>
     <row r="46">
@@ -3082,16 +3082,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>66183</v>
+        <v>65916</v>
       </c>
       <c r="G46" t="n">
         <v>20609</v>
       </c>
       <c r="H46" t="n">
-        <v>45575</v>
+        <v>45307</v>
       </c>
       <c r="I46" t="n">
-        <v>68.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="J46" t="n">
         <v>11.3</v>
@@ -3100,13 +3100,13 @@
         <v>8.1</v>
       </c>
       <c r="L46" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="M46" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="N46" t="n">
-        <v>204467</v>
+        <v>200670</v>
       </c>
     </row>
     <row r="47">
@@ -3128,31 +3128,31 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>100296</v>
+        <v>99843</v>
       </c>
       <c r="G47" t="n">
         <v>23138</v>
       </c>
       <c r="H47" t="n">
-        <v>77158</v>
+        <v>76705</v>
       </c>
       <c r="I47" t="n">
-        <v>76.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="J47" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="K47" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L47" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M47" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>697076</v>
+        <v>690647</v>
       </c>
     </row>
     <row r="48">
@@ -3174,31 +3174,31 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>60033</v>
+        <v>59765</v>
       </c>
       <c r="G48" t="n">
         <v>14458</v>
       </c>
       <c r="H48" t="n">
-        <v>45575</v>
+        <v>45307</v>
       </c>
       <c r="I48" t="n">
-        <v>75.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="J48" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="K48" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="L48" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="M48" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="N48" t="n">
-        <v>95753</v>
+        <v>91956</v>
       </c>
     </row>
     <row r="49">
@@ -3220,31 +3220,31 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>93377</v>
+        <v>92924</v>
       </c>
       <c r="G49" t="n">
         <v>16219</v>
       </c>
       <c r="H49" t="n">
-        <v>77158</v>
+        <v>76705</v>
       </c>
       <c r="I49" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="J49" t="n">
         <v>8</v>
       </c>
       <c r="K49" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L49" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="M49" t="n">
         <v>10.3</v>
       </c>
       <c r="N49" t="n">
-        <v>574774</v>
+        <v>568345</v>
       </c>
     </row>
   </sheetData>
@@ -3259,7 +3259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3335,27 +3335,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.5679</v>
+        <v>4.0638</v>
       </c>
       <c r="C2" t="n">
-        <v>3177</v>
+        <v>3507</v>
       </c>
       <c r="D2" t="n">
-        <v>2178</v>
+        <v>2410</v>
       </c>
       <c r="E2" t="n">
-        <v>981</v>
+        <v>1097</v>
       </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2025-12.xlsx</t>
+          <t>data/raw/tns_microgen/2024-12.xlsx</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -3382,27 +3382,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5329</v>
+        <v>4.8092</v>
       </c>
       <c r="C3" t="n">
-        <v>10876</v>
+        <v>4652</v>
       </c>
       <c r="D3" t="n">
-        <v>3970</v>
+        <v>2418</v>
       </c>
       <c r="E3" t="n">
-        <v>6903</v>
+        <v>2234</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2025-12.xlsx</t>
+          <t>data/raw/tns_microgen/2024-12.xlsx</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -3429,27 +3429,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.0847</v>
+        <v>4.4687</v>
       </c>
       <c r="C4" t="n">
-        <v>44757</v>
+        <v>21657</v>
       </c>
       <c r="D4" t="n">
-        <v>18630</v>
+        <v>11381</v>
       </c>
       <c r="E4" t="n">
-        <v>25558</v>
+        <v>10276</v>
       </c>
       <c r="F4" t="n">
-        <v>569</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2025-12.xlsx</t>
+          <t>data/raw/tns_microgen/2024-12.xlsx</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -3476,27 +3476,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.9918</v>
+        <v>4.4656</v>
       </c>
       <c r="C5" t="n">
-        <v>72897</v>
+        <v>62089</v>
       </c>
       <c r="D5" t="n">
-        <v>37301</v>
+        <v>36834</v>
       </c>
       <c r="E5" t="n">
-        <v>33787</v>
+        <v>25220</v>
       </c>
       <c r="F5" t="n">
-        <v>1809</v>
+        <v>35</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2025-12.xlsx</t>
+          <t>data/raw/tns_microgen/2024-12.xlsx</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3523,27 +3523,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4393</v>
+        <v>3.7559</v>
       </c>
       <c r="C6" t="n">
-        <v>115664</v>
+        <v>73498</v>
       </c>
       <c r="D6" t="n">
-        <v>69302</v>
+        <v>48049</v>
       </c>
       <c r="E6" t="n">
-        <v>44485</v>
+        <v>25235</v>
       </c>
       <c r="F6" t="n">
-        <v>1877</v>
+        <v>214</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2025-12.xlsx</t>
+          <t>data/raw/tns_microgen/2024-12.xlsx</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3570,27 +3570,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3041</v>
+        <v>4.0504</v>
       </c>
       <c r="C7" t="n">
-        <v>144185</v>
+        <v>83926</v>
       </c>
       <c r="D7" t="n">
-        <v>91602</v>
+        <v>52950</v>
       </c>
       <c r="E7" t="n">
-        <v>51113</v>
+        <v>30850</v>
       </c>
       <c r="F7" t="n">
-        <v>1470</v>
+        <v>126</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2025-12.xlsx</t>
+          <t>data/raw/tns_microgen/2024-12.xlsx</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3617,27 +3617,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.1764</v>
+        <v>4.8585</v>
       </c>
       <c r="C8" t="n">
-        <v>122012</v>
+        <v>68856</v>
       </c>
       <c r="D8" t="n">
-        <v>70546</v>
+        <v>42081</v>
       </c>
       <c r="E8" t="n">
-        <v>48073</v>
+        <v>25028</v>
       </c>
       <c r="F8" t="n">
-        <v>3393</v>
+        <v>1747</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2025-12.xlsx</t>
+          <t>data/raw/tns_microgen/2024-12.xlsx</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3664,27 +3664,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.4237</v>
+        <v>4.5573</v>
       </c>
       <c r="C9" t="n">
-        <v>135391</v>
+        <v>74201</v>
       </c>
       <c r="D9" t="n">
-        <v>79633</v>
+        <v>42555</v>
       </c>
       <c r="E9" t="n">
-        <v>53030</v>
+        <v>30238</v>
       </c>
       <c r="F9" t="n">
-        <v>2728</v>
+        <v>1408</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2025-12.xlsx</t>
+          <t>data/raw/tns_microgen/2024-12.xlsx</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3711,27 +3711,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.4868</v>
+        <v>4.7792</v>
       </c>
       <c r="C10" t="n">
-        <v>130771</v>
+        <v>54839</v>
       </c>
       <c r="D10" t="n">
-        <v>66404</v>
+        <v>28248</v>
       </c>
       <c r="E10" t="n">
-        <v>61254</v>
+        <v>25374</v>
       </c>
       <c r="F10" t="n">
-        <v>3113</v>
+        <v>1217</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2025-12.xlsx</t>
+          <t>data/raw/tns_microgen/2024-12.xlsx</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3758,27 +3758,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.6809</v>
+        <v>4.9951</v>
       </c>
       <c r="C11" t="n">
-        <v>70770</v>
+        <v>34940</v>
       </c>
       <c r="D11" t="n">
-        <v>31522</v>
+        <v>12721</v>
       </c>
       <c r="E11" t="n">
-        <v>36509</v>
+        <v>21689</v>
       </c>
       <c r="F11" t="n">
-        <v>2739</v>
+        <v>530</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2025-12.xlsx</t>
+          <t>data/raw/tns_microgen/2024-12.xlsx</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3805,27 +3805,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.3688</v>
+        <v>5.4819</v>
       </c>
       <c r="C12" t="n">
-        <v>36815</v>
+        <v>8917</v>
       </c>
       <c r="D12" t="n">
-        <v>13035</v>
+        <v>2868</v>
       </c>
       <c r="E12" t="n">
-        <v>22400</v>
+        <v>6016</v>
       </c>
       <c r="F12" t="n">
-        <v>1380</v>
+        <v>33</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2025-12.xlsx</t>
+          <t>data/raw/tns_microgen/2024-12.xlsx</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3852,27 +3852,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.987</v>
+        <v>3.9841</v>
       </c>
       <c r="C13" t="n">
-        <v>11227</v>
+        <v>1103</v>
       </c>
       <c r="D13" t="n">
-        <v>4373</v>
+        <v>848</v>
       </c>
       <c r="E13" t="n">
-        <v>6362</v>
+        <v>253</v>
       </c>
       <c r="F13" t="n">
-        <v>492</v>
+        <v>2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2025-12.xlsx</t>
+          <t>data/raw/tns_microgen/2024-12.xlsx</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3899,27 +3899,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.1625</v>
+        <v>4.5679</v>
       </c>
       <c r="C14" t="n">
-        <v>8335.296</v>
+        <v>3177</v>
       </c>
       <c r="D14" t="n">
-        <v>3322.571</v>
+        <v>2178</v>
       </c>
       <c r="E14" t="n">
-        <v>4430</v>
+        <v>981</v>
       </c>
       <c r="F14" t="n">
-        <v>582.725</v>
+        <v>18</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+          <t>data/raw/tns_microgen/2025-12.xlsx</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -3946,27 +3946,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.4292</v>
+        <v>5.5329</v>
       </c>
       <c r="C15" t="n">
-        <v>26363.076</v>
+        <v>10876</v>
       </c>
       <c r="D15" t="n">
-        <v>7981.389</v>
+        <v>3970</v>
       </c>
       <c r="E15" t="n">
-        <v>17457.369</v>
+        <v>6903</v>
       </c>
       <c r="F15" t="n">
-        <v>924.318</v>
+        <v>3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+          <t>data/raw/tns_microgen/2025-12.xlsx</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -3993,27 +3993,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.4217</v>
+        <v>5.0847</v>
       </c>
       <c r="C16" t="n">
-        <v>125111.779</v>
+        <v>44757</v>
       </c>
       <c r="D16" t="n">
-        <v>53815.936</v>
+        <v>18630</v>
       </c>
       <c r="E16" t="n">
-        <v>69381.44</v>
+        <v>25558</v>
       </c>
       <c r="F16" t="n">
-        <v>1914.403</v>
+        <v>569</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+          <t>data/raw/tns_microgen/2025-12.xlsx</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4040,27 +4040,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.749</v>
+        <v>4.9918</v>
       </c>
       <c r="C17" t="n">
-        <v>206939.667</v>
+        <v>72897</v>
       </c>
       <c r="D17" t="n">
-        <v>110500.413</v>
+        <v>37301</v>
       </c>
       <c r="E17" t="n">
-        <v>94363.762</v>
+        <v>33787</v>
       </c>
       <c r="F17" t="n">
-        <v>2075.492</v>
+        <v>1809</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+          <t>data/raw/tns_microgen/2025-12.xlsx</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4087,27 +4087,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.6628</v>
+        <v>4.4393</v>
       </c>
       <c r="C18" t="n">
-        <v>335719.113</v>
+        <v>115664</v>
       </c>
       <c r="D18" t="n">
-        <v>179097.966</v>
+        <v>69302</v>
       </c>
       <c r="E18" t="n">
-        <v>153904.922</v>
+        <v>44485</v>
       </c>
       <c r="F18" t="n">
-        <v>2716.225</v>
+        <v>1877</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+          <t>data/raw/tns_microgen/2025-12.xlsx</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -4134,27 +4134,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.7072</v>
+        <v>4.3041</v>
       </c>
       <c r="C19" t="n">
-        <v>451696.648</v>
+        <v>144185</v>
       </c>
       <c r="D19" t="n">
-        <v>240112.124</v>
+        <v>91602</v>
       </c>
       <c r="E19" t="n">
-        <v>208866.97</v>
+        <v>51113</v>
       </c>
       <c r="F19" t="n">
-        <v>2717.554</v>
+        <v>1470</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+          <t>data/raw/tns_microgen/2025-12.xlsx</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -4181,27 +4181,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.7561</v>
+        <v>5.1764</v>
       </c>
       <c r="C20" t="n">
-        <v>427225.398</v>
+        <v>122012</v>
       </c>
       <c r="D20" t="n">
-        <v>213568.501</v>
+        <v>70546</v>
       </c>
       <c r="E20" t="n">
-        <v>207865.604</v>
+        <v>48073</v>
       </c>
       <c r="F20" t="n">
-        <v>5791.293</v>
+        <v>3393</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+          <t>data/raw/tns_microgen/2025-12.xlsx</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -4228,52 +4228,616 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5.4237</v>
+      </c>
+      <c r="C21" t="n">
+        <v>135391</v>
+      </c>
+      <c r="D21" t="n">
+        <v>79633</v>
+      </c>
+      <c r="E21" t="n">
+        <v>53030</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2728</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>data/raw/tns_microgen/2025-12.xlsx</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ПАО «ТНС энерго Кубань»</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>п. 52в Стандартов раскрытия информации (ПП РФ от 21.01.2004 № 24)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/disclosure/raskrytie-informatsii-subektom-rynka-elektricheskoy-energii-moshchnosti/market-report-gp/informatsiya-ob-obemakh-i-srednevzveshennoy-tsene-pokupki-na-roznichnom-rynke-elektricheskoy-energii/</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5.4868</v>
+      </c>
+      <c r="C22" t="n">
+        <v>130771</v>
+      </c>
+      <c r="D22" t="n">
+        <v>66404</v>
+      </c>
+      <c r="E22" t="n">
+        <v>61254</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3113</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>data/raw/tns_microgen/2025-12.xlsx</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ПАО «ТНС энерго Кубань»</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>п. 52в Стандартов раскрытия информации (ПП РФ от 21.01.2004 № 24)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/disclosure/raskrytie-informatsii-subektom-rynka-elektricheskoy-energii-moshchnosti/market-report-gp/informatsiya-ob-obemakh-i-srednevzveshennoy-tsene-pokupki-na-roznichnom-rynke-elektricheskoy-energii/</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5.6809</v>
+      </c>
+      <c r="C23" t="n">
+        <v>70770</v>
+      </c>
+      <c r="D23" t="n">
+        <v>31522</v>
+      </c>
+      <c r="E23" t="n">
+        <v>36509</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2739</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>data/raw/tns_microgen/2025-12.xlsx</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ПАО «ТНС энерго Кубань»</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>п. 52в Стандартов раскрытия информации (ПП РФ от 21.01.2004 № 24)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/disclosure/raskrytie-informatsii-subektom-rynka-elektricheskoy-energii-moshchnosti/market-report-gp/informatsiya-ob-obemakh-i-srednevzveshennoy-tsene-pokupki-na-roznichnom-rynke-elektricheskoy-energii/</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>6.3688</v>
+      </c>
+      <c r="C24" t="n">
+        <v>36815</v>
+      </c>
+      <c r="D24" t="n">
+        <v>13035</v>
+      </c>
+      <c r="E24" t="n">
+        <v>22400</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1380</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>data/raw/tns_microgen/2025-12.xlsx</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ПАО «ТНС энерго Кубань»</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>п. 52в Стандартов раскрытия информации (ПП РФ от 21.01.2004 № 24)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/disclosure/raskrytie-informatsii-subektom-rynka-elektricheskoy-energii-moshchnosti/market-report-gp/informatsiya-ob-obemakh-i-srednevzveshennoy-tsene-pokupki-na-roznichnom-rynke-elektricheskoy-energii/</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5.987</v>
+      </c>
+      <c r="C25" t="n">
+        <v>11227</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4373</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6362</v>
+      </c>
+      <c r="F25" t="n">
+        <v>492</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>data/raw/tns_microgen/2025-12.xlsx</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ПАО «ТНС энерго Кубань»</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>п. 52в Стандартов раскрытия информации (ПП РФ от 21.01.2004 № 24)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/disclosure/raskrytie-informatsii-subektom-rynka-elektricheskoy-energii-moshchnosti/market-report-gp/informatsiya-ob-obemakh-i-srednevzveshennoy-tsene-pokupki-na-roznichnom-rynke-elektricheskoy-energii/</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>6.1625</v>
+      </c>
+      <c r="C26" t="n">
+        <v>8335.296</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3322.571</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4430</v>
+      </c>
+      <c r="F26" t="n">
+        <v>582.725</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ПАО «ТНС энерго Кубань»</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>п. 52в Стандартов раскрытия информации (ПП РФ от 21.01.2004 № 24)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/disclosure/raskrytie-informatsii-subektom-rynka-elektricheskoy-energii-moshchnosti/market-report-gp/informatsiya-ob-obemakh-i-srednevzveshennoy-tsene-pokupki-na-roznichnom-rynke-elektricheskoy-energii/</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>6.4292</v>
+      </c>
+      <c r="C27" t="n">
+        <v>26363.076</v>
+      </c>
+      <c r="D27" t="n">
+        <v>7981.389</v>
+      </c>
+      <c r="E27" t="n">
+        <v>17457.369</v>
+      </c>
+      <c r="F27" t="n">
+        <v>924.318</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ПАО «ТНС энерго Кубань»</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>п. 52в Стандартов раскрытия информации (ПП РФ от 21.01.2004 № 24)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/disclosure/raskrytie-informatsii-subektom-rynka-elektricheskoy-energii-moshchnosti/market-report-gp/informatsiya-ob-obemakh-i-srednevzveshennoy-tsene-pokupki-na-roznichnom-rynke-elektricheskoy-energii/</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>6.4217</v>
+      </c>
+      <c r="C28" t="n">
+        <v>125111.779</v>
+      </c>
+      <c r="D28" t="n">
+        <v>53815.936</v>
+      </c>
+      <c r="E28" t="n">
+        <v>69381.44</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1914.403</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ПАО «ТНС энерго Кубань»</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>п. 52в Стандартов раскрытия информации (ПП РФ от 21.01.2004 № 24)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/disclosure/raskrytie-informatsii-subektom-rynka-elektricheskoy-energii-moshchnosti/market-report-gp/informatsiya-ob-obemakh-i-srednevzveshennoy-tsene-pokupki-na-roznichnom-rynke-elektricheskoy-energii/</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>5.749</v>
+      </c>
+      <c r="C29" t="n">
+        <v>206939.667</v>
+      </c>
+      <c r="D29" t="n">
+        <v>110500.413</v>
+      </c>
+      <c r="E29" t="n">
+        <v>94363.762</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2075.492</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ПАО «ТНС энерго Кубань»</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>п. 52в Стандартов раскрытия информации (ПП РФ от 21.01.2004 № 24)</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/disclosure/raskrytie-informatsii-subektom-rynka-elektricheskoy-energii-moshchnosti/market-report-gp/informatsiya-ob-obemakh-i-srednevzveshennoy-tsene-pokupki-na-roznichnom-rynke-elektricheskoy-energii/</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5.6628</v>
+      </c>
+      <c r="C30" t="n">
+        <v>335719.113</v>
+      </c>
+      <c r="D30" t="n">
+        <v>179097.966</v>
+      </c>
+      <c r="E30" t="n">
+        <v>153904.922</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2716.225</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ПАО «ТНС энерго Кубань»</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>п. 52в Стандартов раскрытия информации (ПП РФ от 21.01.2004 № 24)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/disclosure/raskrytie-informatsii-subektom-rynka-elektricheskoy-energii-moshchnosti/market-report-gp/informatsiya-ob-obemakh-i-srednevzveshennoy-tsene-pokupki-na-roznichnom-rynke-elektricheskoy-energii/</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5.7072</v>
+      </c>
+      <c r="C31" t="n">
+        <v>451696.648</v>
+      </c>
+      <c r="D31" t="n">
+        <v>240112.124</v>
+      </c>
+      <c r="E31" t="n">
+        <v>208866.97</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2717.554</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ПАО «ТНС энерго Кубань»</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>п. 52в Стандартов раскрытия информации (ПП РФ от 21.01.2004 № 24)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/disclosure/raskrytie-informatsii-subektom-rynka-elektricheskoy-energii-moshchnosti/market-report-gp/informatsiya-ob-obemakh-i-srednevzveshennoy-tsene-pokupki-na-roznichnom-rynke-elektricheskoy-energii/</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>5.7561</v>
+      </c>
+      <c r="C32" t="n">
+        <v>427225.398</v>
+      </c>
+      <c r="D32" t="n">
+        <v>213568.501</v>
+      </c>
+      <c r="E32" t="n">
+        <v>207865.604</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5791.293</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ПАО «ТНС энерго Кубань»</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>п. 52в Стандартов раскрытия информации (ПП РФ от 21.01.2004 № 24)</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/disclosure/raskrytie-informatsii-subektom-rynka-elektricheskoy-energii-moshchnosti/market-report-gp/informatsiya-ob-obemakh-i-srednevzveshennoy-tsene-pokupki-na-roznichnom-rynke-elektricheskoy-energii/</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B33" t="n">
         <v>5.962</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C33" t="n">
         <v>429014.698</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D33" t="n">
         <v>200178.38</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E33" t="n">
         <v>222290.596</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F33" t="n">
         <v>6545.722</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>data/raw/tns_microgen/2026-08.xlsx</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>ПАО «ТНС энерго Кубань»</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>п. 52в Стандартов раскрытия информации (ПП РФ от 21.01.2004 № 24)</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>https://kuban.tns-e.ru/disclosure/raskrytie-informatsii-subektom-rynka-elektricheskoy-energii-moshchnosti/market-report-gp/informatsiya-ob-obemakh-i-srednevzveshennoy-tsene-pokupki-na-roznichnom-rynke-elektricheskoy-energii/</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K21"/>
+  <autoFilter ref="A1:K33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/SunCount_data.xlsx
+++ b/SunCount_data.xlsx
@@ -12,12 +12,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="capex_components" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="capex_estimate" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="equipment_offers" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stub_energy_metrics" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stub_energy_metrics_monthly" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tariff_ranges_2026" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tariffs_2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnkey_prices" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stub_payback" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kp_responses" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stub_energy_metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stub_energy_metrics_monthly" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tariff_ranges_2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tariffs_2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnkey_prices" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stub_payback" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'buyback_by_category'!$A$1:$M$6</definedName>
@@ -25,12 +26,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'capex_components'!$A$1:$J$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'capex_estimate'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'equipment_offers'!$A$1:$Q$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'stub_energy_metrics'!$A$1:$L$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'stub_energy_metrics_monthly'!$A$1:$M$145</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'tariff_ranges_2026'!$A$1:$H$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'tariffs_2026'!$A$1:$M$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'turnkey_prices'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'stub_payback'!$A$1:$N$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'kp_responses'!$A$1:$Q$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'stub_energy_metrics'!$A$1:$L$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'stub_energy_metrics_monthly'!$A$1:$M$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'tariff_ranges_2026'!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'tariffs_2026'!$A$1:$M$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'turnkey_prices'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'stub_payback'!$A$1:$N$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -771,6 +773,4783 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="59" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date_from</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>date_to</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>category_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>tariff_type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>hours</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>price_rub_kwh</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vat_included</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>accessed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0-24</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0-24</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>7-23</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7-23</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7-10,17-21</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7-10,17-21</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>semipeak</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>10-17,21-23</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>semipeak</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>10-17,21-23</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0-24</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0-24</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>7-23</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>7-23</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>7-10,17-21</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>7-10,17-21</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>semipeak</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>10-17,21-23</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>semipeak</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>10-17,21-23</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0-24</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0-24</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>7-23</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>7-23</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>7-10,17-21</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>7-10,17-21</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>semipeak</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>10-17,21-23</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>semipeak</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>10-17,21-23</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0-24</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0-24</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>7-23</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>7-23</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>7-10,17-21</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>7-10,17-21</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>semipeak</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>10-17,21-23</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>semipeak</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>10-17,21-23</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0-24</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0-24</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>7-23</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>7-23</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>7-10,17-21</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>8</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>7-10,17-21</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>semipeak</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>10-17,21-23</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>semipeak</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>10-17,21-23</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0-24</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>0-24</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>7-23</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>7-23</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>two_zone</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>7-10,17-21</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>7-10,17-21</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>semipeak</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>10-17,21-23</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>semipeak</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>10-17,21-23</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>reduced</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>three_zone</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>23-7</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M73"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -940,7 +5719,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6614,6 +11393,298 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>offer_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>date_collected</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pv_kw</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>panel_model</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>panel_count</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>inverter_model</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>inverter_type</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>price_equipment_rub</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>price_install_rub</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>price_total_rub</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>includes_meter</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>includes_grid_connection</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>warranty_years</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ekoproekt_3</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Экопроект-Энерго</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Краснодар</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://ekoproekt-energo.ru</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>630 Вт</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>on-grid</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>150000</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ответ на запрос КП от 15.10.2026 (e-mail, 20.10.2026). Цена базового комплекта оборудования. Монтаж — 15–25 % от стоимости комплекта + расходники (кабель переменного тока, щиток, кабель-канал). Платёж за подключение микрогенерации «порядка 70–77 тыс. ₽» — со слов компании, подтвердить (T2.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ekoproekt_6</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Экопроект-Энерго</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Краснодар</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://ekoproekt-energo.ru</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>on-grid</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>261000</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Тот же ответ. Цена базового комплекта; монтаж и подключение — как в строке ekoproekt_3. Компания: «10 кВт практически не применяется, как правило техусловия подключения 15 кВт»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ekoproekt_15</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Экопроект-Энерго</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Краснодар</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://ekoproekt-energo.ru</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>on-grid (3 фазы)</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>620000</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Тот же ответ. Цена базового комплекта; монтаж и подключение — как в строке ekoproekt_3. Опция: защита от импульсных перенапряжений AC/DC (не обязательна). Обслуживание: раз в год подтянуть соединения, при сильной запылённости помыть панели</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7203,7 +12274,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13780,7 +18851,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14073,4781 +19144,4 @@
   <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M73"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="59" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>date_from</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>date_to</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>category_name</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>tariff_type</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>zone</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>hours</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>range</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>price_rub_kwh</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>vat_included</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>document</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>source_url</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>accessed</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0-24</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0-24</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>7-23</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>7-23</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>7-10,17-21</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>7-10,17-21</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>9.34</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>semipeak</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>10-17,21-23</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>semipeak</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>10-17,21-23</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0-24</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0-24</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>7-23</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>11.41</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>7-23</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>13.13</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>7-10,17-21</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>7-10,17-21</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>semipeak</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>10-17,21-23</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>semipeak</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>10-17,21-23</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>0-24</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>14.88</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0-24</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>17.84</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>7-23</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>7-23</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>20.02</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>8.93</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>10.68</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>7-10,17-21</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>7-10,17-21</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>semipeak</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>10-17,21-23</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>14.88</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>semipeak</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>10-17,21-23</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>17.84</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>8.93</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Раздел 1: городское население (газ. плиты, иные случаи)</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>10.68</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>0-24</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>0-24</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>7-23</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>7-23</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>7-10,17-21</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>7-10,17-21</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>semipeak</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>10-17,21-23</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>semipeak</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>10-17,21-23</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>0-24</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>0-24</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>7-23</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>7-23</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>9.19</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>7-10,17-21</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>8</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>7-10,17-21</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I57" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>semipeak</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>10-17,21-23</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>semipeak</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>10-17,21-23</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="I61" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>0-24</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I62" t="n">
-        <v>14.88</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>0-24</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I63" t="n">
-        <v>17.84</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>7-23</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I64" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>7-23</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I65" t="n">
-        <v>20.02</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I66" t="n">
-        <v>8.93</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>two_zone</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I67" t="n">
-        <v>10.68</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>7-10,17-21</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I68" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>7-10,17-21</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I69" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>semipeak</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>10-17,21-23</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I70" t="n">
-        <v>14.88</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>semipeak</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>10-17,21-23</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I71" t="n">
-        <v>17.84</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I72" t="n">
-        <v>8.93</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>reduced</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Разделы 2–8: сельское население; город с электроплитами/электроотоплением</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>three_zone</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>23-7</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="I73" t="n">
-        <v>10.68</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Приказ ДГРТ Краснодарского края от 17.12.2025 № 18/2025-э (Краснодарский край, Республика Адыгея, ФТ «Сириус»)</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:M73"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/SunCount_data.xlsx
+++ b/SunCount_data.xlsx
@@ -22,9 +22,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'buyback_by_category'!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'buyback_prices'!$A$1:$K$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'capex_components'!$A$1:$J$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'capex_estimate'!$A$1:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'buyback_prices'!$A$1:$K$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'capex_components'!$A$1:$J$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'capex_estimate'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'equipment_offers'!$A$1:$Q$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'kp_responses'!$A$1:$Q$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'stub_energy_metrics'!$A$1:$L$13</definedName>
@@ -32,7 +32,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'tariff_ranges_2026'!$A$1:$H$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'tariffs_2026'!$A$1:$M$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'turnkey_prices'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'stub_payback'!$A$1:$N$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'stub_payback'!$A$1:$R$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -730,9 +730,15 @@
       <c r="C6" t="n">
         <v>7.8967</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>6.5347</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6.431</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.6127</v>
+      </c>
       <c r="G6" t="n">
         <v>2263.42</v>
       </c>
@@ -5725,7 +5731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5742,6 +5748,10 @@
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5815,13 +5825,33 @@
           <t>npv_rub</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>effect_net_rub</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>export_share_net_pct</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>simple_payback_net</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>disc_payback_net</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C2" t="n">
         <v>20</v>
@@ -5835,31 +5865,43 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>19773</v>
+        <v>19657</v>
       </c>
       <c r="G2" t="n">
         <v>6181</v>
       </c>
       <c r="H2" t="n">
-        <v>13592</v>
+        <v>13476</v>
       </c>
       <c r="I2" t="n">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="K2" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="M2" t="n">
-        <v>22.1</v>
+        <v>24.6</v>
       </c>
       <c r="N2" t="n">
-        <v>21448</v>
+        <v>2797</v>
+      </c>
+      <c r="O2" t="n">
+        <v>30912</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="R2" t="n">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -5867,7 +5909,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C3" t="n">
         <v>20</v>
@@ -5881,31 +5923,43 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>29952</v>
+        <v>29754</v>
       </c>
       <c r="G3" t="n">
         <v>6940</v>
       </c>
       <c r="H3" t="n">
-        <v>23012</v>
+        <v>22815</v>
       </c>
       <c r="I3" t="n">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
       <c r="J3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="K3" t="n">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="L3" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="M3" t="n">
-        <v>10.6</v>
+        <v>13.5</v>
       </c>
       <c r="N3" t="n">
-        <v>168441</v>
+        <v>148646</v>
+      </c>
+      <c r="O3" t="n">
+        <v>34087</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R3" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="4">
@@ -5913,7 +5967,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C4" t="n">
         <v>20</v>
@@ -5927,25 +5981,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>17929</v>
+        <v>17812</v>
       </c>
       <c r="G4" t="n">
         <v>4336</v>
       </c>
       <c r="H4" t="n">
-        <v>13592</v>
+        <v>13476</v>
       </c>
       <c r="I4" t="n">
-        <v>75.8</v>
+        <v>75.7</v>
       </c>
       <c r="J4" t="n">
-        <v>13.9</v>
+        <v>14.9</v>
       </c>
       <c r="K4" t="n">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="L4" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -5953,7 +6007,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>-11157</v>
+        <v>-29808</v>
+      </c>
+      <c r="O4" t="n">
+        <v>21686</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>16.8</v>
       </c>
     </row>
     <row r="5">
@@ -5961,7 +6027,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C5" t="n">
         <v>20</v>
@@ -5975,31 +6041,43 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>27876</v>
+        <v>27679</v>
       </c>
       <c r="G5" t="n">
         <v>4864</v>
       </c>
       <c r="H5" t="n">
-        <v>23012</v>
+        <v>22815</v>
       </c>
       <c r="I5" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="K5" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="L5" t="n">
         <v>13.5</v>
       </c>
       <c r="M5" t="n">
-        <v>13.9</v>
+        <v>15.2</v>
       </c>
       <c r="N5" t="n">
-        <v>131760</v>
+        <v>111965</v>
+      </c>
+      <c r="O5" t="n">
+        <v>24671</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>14.5</v>
       </c>
     </row>
     <row r="6">
@@ -6007,7 +6085,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C6" t="n">
         <v>30</v>
@@ -6021,31 +6099,43 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>21166</v>
+        <v>21065</v>
       </c>
       <c r="G6" t="n">
         <v>9273</v>
       </c>
       <c r="H6" t="n">
-        <v>11893</v>
+        <v>11791</v>
       </c>
       <c r="I6" t="n">
-        <v>56.2</v>
+        <v>56</v>
       </c>
       <c r="J6" t="n">
-        <v>11.8</v>
+        <v>12.6</v>
       </c>
       <c r="K6" t="n">
-        <v>9.4</v>
+        <v>10.3</v>
       </c>
       <c r="L6" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="M6" t="n">
-        <v>18.9</v>
+        <v>20.9</v>
       </c>
       <c r="N6" t="n">
-        <v>52011</v>
+        <v>33566</v>
+      </c>
+      <c r="O6" t="n">
+        <v>30912</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -6053,7 +6143,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C7" t="n">
         <v>30</v>
@@ -6067,31 +6157,43 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>30547</v>
+        <v>30374</v>
       </c>
       <c r="G7" t="n">
         <v>10411</v>
       </c>
       <c r="H7" t="n">
-        <v>20135</v>
+        <v>19963</v>
       </c>
       <c r="I7" t="n">
-        <v>65.90000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="J7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="L7" t="n">
         <v>12.3</v>
       </c>
       <c r="M7" t="n">
-        <v>10.1</v>
+        <v>12.7</v>
       </c>
       <c r="N7" t="n">
-        <v>189015</v>
+        <v>169568</v>
+      </c>
+      <c r="O7" t="n">
+        <v>34088</v>
+      </c>
+      <c r="P7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="8">
@@ -6099,7 +6201,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C8" t="n">
         <v>30</v>
@@ -6113,31 +6215,45 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>18399</v>
+        <v>18297</v>
       </c>
       <c r="G8" t="n">
         <v>6506</v>
       </c>
       <c r="H8" t="n">
-        <v>11893</v>
+        <v>11791</v>
       </c>
       <c r="I8" t="n">
-        <v>64.59999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="K8" t="n">
-        <v>10.9</v>
+        <v>11.9</v>
       </c>
       <c r="L8" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>24.5</v>
+        <v>20.5</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="N8" t="n">
-        <v>3094</v>
+        <v>-15351</v>
+      </c>
+      <c r="O8" t="n">
+        <v>21687</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>16.8</v>
       </c>
     </row>
     <row r="9">
@@ -6145,7 +6261,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C9" t="n">
         <v>30</v>
@@ -6159,31 +6275,43 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>27433</v>
+        <v>27261</v>
       </c>
       <c r="G9" t="n">
         <v>7298</v>
       </c>
       <c r="H9" t="n">
-        <v>20135</v>
+        <v>19963</v>
       </c>
       <c r="I9" t="n">
-        <v>73.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J9" t="n">
-        <v>9.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="M9" t="n">
-        <v>13.8</v>
+        <v>15.1</v>
       </c>
       <c r="N9" t="n">
-        <v>133983</v>
+        <v>114537</v>
+      </c>
+      <c r="O9" t="n">
+        <v>24672</v>
+      </c>
+      <c r="P9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>14.5</v>
       </c>
     </row>
     <row r="10">
@@ -6191,7 +6319,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C10" t="n">
         <v>40</v>
@@ -6205,31 +6333,43 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>22560</v>
+        <v>22473</v>
       </c>
       <c r="G10" t="n">
         <v>12366</v>
       </c>
       <c r="H10" t="n">
-        <v>10194</v>
+        <v>10106</v>
       </c>
       <c r="I10" t="n">
-        <v>45.2</v>
+        <v>45</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>11.8</v>
       </c>
       <c r="K10" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="M10" t="n">
-        <v>16.7</v>
+        <v>18.2</v>
       </c>
       <c r="N10" t="n">
-        <v>82579</v>
+        <v>64341</v>
+      </c>
+      <c r="O10" t="n">
+        <v>30913</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -6237,7 +6377,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C11" t="n">
         <v>40</v>
@@ -6251,31 +6391,43 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>31142</v>
+        <v>30994</v>
       </c>
       <c r="G11" t="n">
         <v>13884</v>
       </c>
       <c r="H11" t="n">
-        <v>17258</v>
+        <v>17110</v>
       </c>
       <c r="I11" t="n">
-        <v>55.4</v>
+        <v>55.2</v>
       </c>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="K11" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="L11" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="M11" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="N11" t="n">
-        <v>209591</v>
+        <v>190495</v>
+      </c>
+      <c r="O11" t="n">
+        <v>34089</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R11" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="12">
@@ -6283,7 +6435,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C12" t="n">
         <v>40</v>
@@ -6297,31 +6449,45 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18869</v>
+        <v>18782</v>
       </c>
       <c r="G12" t="n">
         <v>8676</v>
       </c>
       <c r="H12" t="n">
-        <v>10194</v>
+        <v>10106</v>
       </c>
       <c r="I12" t="n">
-        <v>54</v>
+        <v>53.8</v>
       </c>
       <c r="J12" t="n">
-        <v>13.2</v>
+        <v>14.2</v>
       </c>
       <c r="K12" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="L12" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M12" t="n">
-        <v>22.6</v>
+        <v>20</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="N12" t="n">
-        <v>17347</v>
+        <v>-891</v>
+      </c>
+      <c r="O12" t="n">
+        <v>21688</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>16.8</v>
       </c>
     </row>
     <row r="13">
@@ -6329,7 +6495,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C13" t="n">
         <v>40</v>
@@ -6343,31 +6509,43 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>26990</v>
+        <v>26842</v>
       </c>
       <c r="G13" t="n">
         <v>9732</v>
       </c>
       <c r="H13" t="n">
-        <v>17258</v>
+        <v>17110</v>
       </c>
       <c r="I13" t="n">
-        <v>63.9</v>
+        <v>63.7</v>
       </c>
       <c r="J13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="K13" t="n">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="L13" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="M13" t="n">
-        <v>13.7</v>
+        <v>15</v>
       </c>
       <c r="N13" t="n">
-        <v>136204</v>
+        <v>117108</v>
+      </c>
+      <c r="O13" t="n">
+        <v>24673</v>
+      </c>
+      <c r="P13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>14.5</v>
       </c>
     </row>
     <row r="14">
@@ -6375,7 +6553,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C14" t="n">
         <v>50</v>
@@ -6389,31 +6567,43 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>23951</v>
+        <v>23878</v>
       </c>
       <c r="G14" t="n">
         <v>15456</v>
       </c>
       <c r="H14" t="n">
-        <v>8495</v>
+        <v>8422</v>
       </c>
       <c r="I14" t="n">
-        <v>35.5</v>
+        <v>35.3</v>
       </c>
       <c r="J14" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="K14" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="L14" t="n">
         <v>15.7</v>
       </c>
       <c r="M14" t="n">
-        <v>14.9</v>
+        <v>16.2</v>
       </c>
       <c r="N14" t="n">
-        <v>113097</v>
+        <v>95065</v>
+      </c>
+      <c r="O14" t="n">
+        <v>30912</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -6421,7 +6611,7 @@
         <v>3</v>
       </c>
       <c r="B15" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C15" t="n">
         <v>50</v>
@@ -6435,31 +6625,43 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>31735</v>
+        <v>31611</v>
       </c>
       <c r="G15" t="n">
         <v>17353</v>
       </c>
       <c r="H15" t="n">
-        <v>14382</v>
+        <v>14258</v>
       </c>
       <c r="I15" t="n">
-        <v>45.3</v>
+        <v>45.1</v>
       </c>
       <c r="J15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L15" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" t="n">
+        <v>211367</v>
+      </c>
+      <c r="O15" t="n">
+        <v>34087</v>
+      </c>
+      <c r="P15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Q15" t="n">
         <v>7.8</v>
       </c>
-      <c r="K15" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="M15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="N15" t="n">
-        <v>230115</v>
+      <c r="R15" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="16">
@@ -6467,7 +6669,7 @@
         <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C16" t="n">
         <v>50</v>
@@ -6481,31 +6683,43 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>19338</v>
+        <v>19265</v>
       </c>
       <c r="G16" t="n">
         <v>10843</v>
       </c>
       <c r="H16" t="n">
-        <v>8495</v>
+        <v>8422</v>
       </c>
       <c r="I16" t="n">
-        <v>43.9</v>
+        <v>43.7</v>
       </c>
       <c r="J16" t="n">
-        <v>12.9</v>
+        <v>13.8</v>
       </c>
       <c r="K16" t="n">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="L16" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="M16" t="n">
-        <v>20.9</v>
+        <v>23.2</v>
       </c>
       <c r="N16" t="n">
-        <v>31567</v>
+        <v>13535</v>
+      </c>
+      <c r="O16" t="n">
+        <v>21686</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>16.8</v>
       </c>
     </row>
     <row r="17">
@@ -6513,7 +6727,7 @@
         <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C17" t="n">
         <v>50</v>
@@ -6527,31 +6741,43 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>26545</v>
+        <v>26422</v>
       </c>
       <c r="G17" t="n">
         <v>12164</v>
       </c>
       <c r="H17" t="n">
-        <v>14382</v>
+        <v>14258</v>
       </c>
       <c r="I17" t="n">
-        <v>54.2</v>
+        <v>54</v>
       </c>
       <c r="J17" t="n">
-        <v>9.4</v>
+        <v>10.1</v>
       </c>
       <c r="K17" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="M17" t="n">
-        <v>13.7</v>
+        <v>14.9</v>
       </c>
       <c r="N17" t="n">
-        <v>138393</v>
+        <v>119645</v>
+      </c>
+      <c r="O17" t="n">
+        <v>24671</v>
+      </c>
+      <c r="P17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>14.5</v>
       </c>
     </row>
     <row r="18">
@@ -6559,7 +6785,7 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C18" t="n">
         <v>60</v>
@@ -6573,31 +6799,43 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>25344</v>
+        <v>25285</v>
       </c>
       <c r="G18" t="n">
         <v>18547</v>
       </c>
       <c r="H18" t="n">
-        <v>6797</v>
+        <v>6738</v>
       </c>
       <c r="I18" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="J18" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="K18" t="n">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="L18" t="n">
         <v>14.8</v>
       </c>
       <c r="M18" t="n">
-        <v>13.5</v>
+        <v>14.6</v>
       </c>
       <c r="N18" t="n">
-        <v>143657</v>
+        <v>125831</v>
+      </c>
+      <c r="O18" t="n">
+        <v>30913</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -6605,7 +6843,7 @@
         <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C19" t="n">
         <v>60</v>
@@ -6619,31 +6857,43 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>32330</v>
+        <v>32232</v>
       </c>
       <c r="G19" t="n">
         <v>20824</v>
       </c>
       <c r="H19" t="n">
-        <v>11507</v>
+        <v>11408</v>
       </c>
       <c r="I19" t="n">
-        <v>35.6</v>
+        <v>35.4</v>
       </c>
       <c r="J19" t="n">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="L19" t="n">
         <v>11.6</v>
       </c>
       <c r="M19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="N19" t="n">
-        <v>250692</v>
+        <v>232294</v>
+      </c>
+      <c r="O19" t="n">
+        <v>34089</v>
+      </c>
+      <c r="P19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R19" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="20">
@@ -6651,7 +6901,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C20" t="n">
         <v>60</v>
@@ -6665,31 +6915,43 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>19809</v>
+        <v>19750</v>
       </c>
       <c r="G20" t="n">
         <v>13012</v>
       </c>
       <c r="H20" t="n">
-        <v>6797</v>
+        <v>6738</v>
       </c>
       <c r="I20" t="n">
-        <v>34.3</v>
+        <v>34.1</v>
       </c>
       <c r="J20" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="K20" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="L20" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="M20" t="n">
-        <v>19.5</v>
+        <v>21.5</v>
       </c>
       <c r="N20" t="n">
-        <v>45819</v>
+        <v>27994</v>
+      </c>
+      <c r="O20" t="n">
+        <v>21688</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>16.8</v>
       </c>
     </row>
     <row r="21">
@@ -6697,7 +6959,7 @@
         <v>3</v>
       </c>
       <c r="B21" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C21" t="n">
         <v>60</v>
@@ -6711,31 +6973,43 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>26103</v>
+        <v>26005</v>
       </c>
       <c r="G21" t="n">
         <v>14597</v>
       </c>
       <c r="H21" t="n">
-        <v>11507</v>
+        <v>11408</v>
       </c>
       <c r="I21" t="n">
-        <v>44.1</v>
+        <v>43.9</v>
       </c>
       <c r="J21" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
       <c r="K21" t="n">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L21" t="n">
         <v>14.4</v>
       </c>
       <c r="M21" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="N21" t="n">
-        <v>140625</v>
+        <v>122227</v>
+      </c>
+      <c r="O21" t="n">
+        <v>24673</v>
+      </c>
+      <c r="P21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="R21" t="n">
+        <v>14.5</v>
       </c>
     </row>
     <row r="22">
@@ -6743,7 +7017,7 @@
         <v>3</v>
       </c>
       <c r="B22" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C22" t="n">
         <v>70</v>
@@ -6757,31 +7031,43 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>26736</v>
+        <v>26692</v>
       </c>
       <c r="G22" t="n">
         <v>21639</v>
       </c>
       <c r="H22" t="n">
-        <v>5097</v>
+        <v>5053</v>
       </c>
       <c r="I22" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="J22" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="K22" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="L22" t="n">
         <v>14</v>
       </c>
       <c r="M22" t="n">
-        <v>10.6</v>
+        <v>13.3</v>
       </c>
       <c r="N22" t="n">
-        <v>174206</v>
+        <v>156587</v>
+      </c>
+      <c r="O22" t="n">
+        <v>30912</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="R22" t="n">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -6789,7 +7075,7 @@
         <v>3</v>
       </c>
       <c r="B23" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C23" t="n">
         <v>70</v>
@@ -6803,31 +7089,43 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>32924</v>
+        <v>32850</v>
       </c>
       <c r="G23" t="n">
         <v>24295</v>
       </c>
       <c r="H23" t="n">
-        <v>8629</v>
+        <v>8555</v>
       </c>
       <c r="I23" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="K23" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="L23" t="n">
         <v>11.4</v>
       </c>
       <c r="M23" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>253196</v>
+      </c>
+      <c r="O23" t="n">
+        <v>34088</v>
+      </c>
+      <c r="P23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R23" t="n">
         <v>8.4</v>
-      </c>
-      <c r="N23" t="n">
-        <v>271244</v>
       </c>
     </row>
     <row r="24">
@@ -6835,7 +7133,7 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C24" t="n">
         <v>70</v>
@@ -6849,31 +7147,43 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>20278</v>
+        <v>20234</v>
       </c>
       <c r="G24" t="n">
         <v>15181</v>
       </c>
       <c r="H24" t="n">
-        <v>5097</v>
+        <v>5053</v>
       </c>
       <c r="I24" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>12.3</v>
+        <v>13.1</v>
       </c>
       <c r="K24" t="n">
-        <v>9.9</v>
+        <v>10.7</v>
       </c>
       <c r="L24" t="n">
         <v>18.5</v>
       </c>
       <c r="M24" t="n">
-        <v>18.3</v>
+        <v>20.1</v>
       </c>
       <c r="N24" t="n">
-        <v>60057</v>
+        <v>42438</v>
+      </c>
+      <c r="O24" t="n">
+        <v>21687</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>16.8</v>
       </c>
     </row>
     <row r="25">
@@ -6881,7 +7191,7 @@
         <v>3</v>
       </c>
       <c r="B25" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C25" t="n">
         <v>70</v>
@@ -6895,31 +7205,43 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>25659</v>
+        <v>25585</v>
       </c>
       <c r="G25" t="n">
         <v>17030</v>
       </c>
       <c r="H25" t="n">
-        <v>8629</v>
+        <v>8555</v>
       </c>
       <c r="I25" t="n">
-        <v>33.6</v>
+        <v>33.4</v>
       </c>
       <c r="J25" t="n">
-        <v>9.699999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="K25" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="L25" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="M25" t="n">
-        <v>13.5</v>
+        <v>14.7</v>
       </c>
       <c r="N25" t="n">
-        <v>142826</v>
+        <v>124778</v>
+      </c>
+      <c r="O25" t="n">
+        <v>24672</v>
+      </c>
+      <c r="P25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="R25" t="n">
+        <v>14.5</v>
       </c>
     </row>
     <row r="26">
@@ -6927,7 +7249,7 @@
         <v>3</v>
       </c>
       <c r="B26" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C26" t="n">
         <v>80</v>
@@ -6941,31 +7263,43 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>28074</v>
+        <v>28043</v>
       </c>
       <c r="G26" t="n">
         <v>24606</v>
       </c>
       <c r="H26" t="n">
-        <v>3468</v>
+        <v>3437</v>
       </c>
       <c r="I26" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="J26" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="K26" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="L26" t="n">
         <v>13.4</v>
       </c>
       <c r="M26" t="n">
-        <v>9.9</v>
+        <v>10.7</v>
       </c>
       <c r="N26" t="n">
-        <v>203544</v>
+        <v>186114</v>
+      </c>
+      <c r="O26" t="n">
+        <v>30912</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -6973,7 +7307,7 @@
         <v>3</v>
       </c>
       <c r="B27" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C27" t="n">
         <v>80</v>
@@ -6987,31 +7321,43 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>33497</v>
+        <v>33446</v>
       </c>
       <c r="G27" t="n">
         <v>27626</v>
       </c>
       <c r="H27" t="n">
-        <v>5871</v>
+        <v>5820</v>
       </c>
       <c r="I27" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="J27" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="K27" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="L27" t="n">
         <v>11.2</v>
       </c>
       <c r="M27" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>291009</v>
+        <v>273282</v>
+      </c>
+      <c r="O27" t="n">
+        <v>34087</v>
+      </c>
+      <c r="P27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R27" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="28">
@@ -7019,7 +7365,7 @@
         <v>3</v>
       </c>
       <c r="B28" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C28" t="n">
         <v>80</v>
@@ -7033,31 +7379,43 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>20730</v>
+        <v>20700</v>
       </c>
       <c r="G28" t="n">
         <v>17263</v>
       </c>
       <c r="H28" t="n">
-        <v>3468</v>
+        <v>3437</v>
       </c>
       <c r="I28" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="J28" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="K28" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="L28" t="n">
         <v>18.1</v>
       </c>
       <c r="M28" t="n">
-        <v>17.3</v>
+        <v>18.9</v>
       </c>
       <c r="N28" t="n">
-        <v>73745</v>
+        <v>56316</v>
+      </c>
+      <c r="O28" t="n">
+        <v>21686</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="R28" t="n">
+        <v>16.8</v>
       </c>
     </row>
     <row r="29">
@@ -7065,7 +7423,7 @@
         <v>3</v>
       </c>
       <c r="B29" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="C29" t="n">
         <v>80</v>
@@ -7079,31 +7437,43 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>25236</v>
+        <v>25185</v>
       </c>
       <c r="G29" t="n">
         <v>19365</v>
       </c>
       <c r="H29" t="n">
-        <v>5871</v>
+        <v>5820</v>
       </c>
       <c r="I29" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="J29" t="n">
-        <v>9.9</v>
+        <v>10.6</v>
       </c>
       <c r="K29" t="n">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="L29" t="n">
         <v>14.9</v>
       </c>
       <c r="M29" t="n">
-        <v>13.4</v>
+        <v>14.6</v>
       </c>
       <c r="N29" t="n">
-        <v>144986</v>
+        <v>127258</v>
+      </c>
+      <c r="O29" t="n">
+        <v>24671</v>
+      </c>
+      <c r="P29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="R29" t="n">
+        <v>14.5</v>
       </c>
     </row>
     <row r="30">
@@ -7111,7 +7481,7 @@
         <v>5</v>
       </c>
       <c r="B30" t="n">
-        <v>402000</v>
+        <v>418000</v>
       </c>
       <c r="C30" t="n">
         <v>20</v>
@@ -7125,31 +7495,43 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>32959</v>
+        <v>32765</v>
       </c>
       <c r="G30" t="n">
         <v>10305</v>
       </c>
       <c r="H30" t="n">
-        <v>22653</v>
+        <v>22459</v>
       </c>
       <c r="I30" t="n">
-        <v>68.7</v>
+        <v>68.5</v>
       </c>
       <c r="J30" t="n">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="K30" t="n">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="L30" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="M30" t="n">
-        <v>19.4</v>
+        <v>20.7</v>
       </c>
       <c r="N30" t="n">
-        <v>71831</v>
+        <v>53079</v>
+      </c>
+      <c r="O30" t="n">
+        <v>47368</v>
+      </c>
+      <c r="P30" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="R30" t="n">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -7157,7 +7539,7 @@
         <v>5</v>
       </c>
       <c r="B31" t="n">
-        <v>402000</v>
+        <v>418000</v>
       </c>
       <c r="C31" t="n">
         <v>20</v>
@@ -7171,31 +7553,43 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>49923</v>
+        <v>49594</v>
       </c>
       <c r="G31" t="n">
         <v>11570</v>
       </c>
       <c r="H31" t="n">
-        <v>38352</v>
+        <v>38024</v>
       </c>
       <c r="I31" t="n">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
       <c r="J31" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="K31" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="L31" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="M31" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="N31" t="n">
-        <v>316822</v>
+        <v>296164</v>
+      </c>
+      <c r="O31" t="n">
+        <v>53887</v>
+      </c>
+      <c r="P31" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R31" t="n">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -7203,7 +7597,7 @@
         <v>5</v>
       </c>
       <c r="B32" t="n">
-        <v>402000</v>
+        <v>418000</v>
       </c>
       <c r="C32" t="n">
         <v>20</v>
@@ -7217,31 +7611,45 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>29883</v>
+        <v>29689</v>
       </c>
       <c r="G32" t="n">
         <v>7230</v>
       </c>
       <c r="H32" t="n">
-        <v>22653</v>
+        <v>22459</v>
       </c>
       <c r="I32" t="n">
-        <v>75.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="K32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="M32" t="n">
-        <v>23.3</v>
+        <v>17.7</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="N32" t="n">
-        <v>17470</v>
+        <v>-1282</v>
+      </c>
+      <c r="O32" t="n">
+        <v>34658</v>
+      </c>
+      <c r="P32" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>16.1</v>
       </c>
     </row>
     <row r="33">
@@ -7249,7 +7657,7 @@
         <v>5</v>
       </c>
       <c r="B33" t="n">
-        <v>402000</v>
+        <v>418000</v>
       </c>
       <c r="C33" t="n">
         <v>20</v>
@@ -7263,31 +7671,43 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>46463</v>
+        <v>46134</v>
       </c>
       <c r="G33" t="n">
         <v>8110</v>
       </c>
       <c r="H33" t="n">
-        <v>38352</v>
+        <v>38024</v>
       </c>
       <c r="I33" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="K33" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="L33" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="M33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="N33" t="n">
-        <v>255666</v>
+        <v>235007</v>
+      </c>
+      <c r="O33" t="n">
+        <v>42849</v>
+      </c>
+      <c r="P33" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="R33" t="n">
+        <v>12.9</v>
       </c>
     </row>
     <row r="34">
@@ -7295,7 +7715,7 @@
         <v>5</v>
       </c>
       <c r="B34" t="n">
-        <v>402000</v>
+        <v>418000</v>
       </c>
       <c r="C34" t="n">
         <v>30</v>
@@ -7309,31 +7729,43 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>35278</v>
+        <v>35108</v>
       </c>
       <c r="G34" t="n">
         <v>15456</v>
       </c>
       <c r="H34" t="n">
-        <v>19822</v>
+        <v>19652</v>
       </c>
       <c r="I34" t="n">
-        <v>56.2</v>
+        <v>56</v>
       </c>
       <c r="J34" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="K34" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="M34" t="n">
-        <v>16.8</v>
+        <v>17.9</v>
       </c>
       <c r="N34" t="n">
-        <v>122719</v>
+        <v>104311</v>
+      </c>
+      <c r="O34" t="n">
+        <v>47367</v>
+      </c>
+      <c r="P34" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="R34" t="n">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -7341,7 +7773,7 @@
         <v>5</v>
       </c>
       <c r="B35" t="n">
-        <v>402000</v>
+        <v>418000</v>
       </c>
       <c r="C35" t="n">
         <v>30</v>
@@ -7355,31 +7787,43 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>50912</v>
+        <v>50624</v>
       </c>
       <c r="G35" t="n">
         <v>17353</v>
       </c>
       <c r="H35" t="n">
-        <v>33559</v>
+        <v>33272</v>
       </c>
       <c r="I35" t="n">
-        <v>65.90000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="J35" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="L35" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="M35" t="n">
-        <v>9.699999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="N35" t="n">
-        <v>351059</v>
+        <v>330983</v>
+      </c>
+      <c r="O35" t="n">
+        <v>53886</v>
+      </c>
+      <c r="P35" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R35" t="n">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -7387,7 +7831,7 @@
         <v>5</v>
       </c>
       <c r="B36" t="n">
-        <v>402000</v>
+        <v>418000</v>
       </c>
       <c r="C36" t="n">
         <v>30</v>
@@ -7401,31 +7845,43 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>30665</v>
+        <v>30496</v>
       </c>
       <c r="G36" t="n">
         <v>10843</v>
       </c>
       <c r="H36" t="n">
-        <v>19822</v>
+        <v>19652</v>
       </c>
       <c r="I36" t="n">
-        <v>64.59999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>13.1</v>
+        <v>13.7</v>
       </c>
       <c r="K36" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="L36" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="M36" t="n">
-        <v>21.4</v>
+        <v>23</v>
       </c>
       <c r="N36" t="n">
-        <v>41189</v>
+        <v>22781</v>
+      </c>
+      <c r="O36" t="n">
+        <v>34658</v>
+      </c>
+      <c r="P36" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>16.1</v>
       </c>
     </row>
     <row r="37">
@@ -7433,7 +7889,7 @@
         <v>5</v>
       </c>
       <c r="B37" t="n">
-        <v>402000</v>
+        <v>418000</v>
       </c>
       <c r="C37" t="n">
         <v>30</v>
@@ -7447,31 +7903,43 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>45723</v>
+        <v>45435</v>
       </c>
       <c r="G37" t="n">
         <v>12164</v>
       </c>
       <c r="H37" t="n">
-        <v>33559</v>
+        <v>33272</v>
       </c>
       <c r="I37" t="n">
-        <v>73.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J37" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="L37" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="M37" t="n">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="N37" t="n">
-        <v>259337</v>
+        <v>239261</v>
+      </c>
+      <c r="O37" t="n">
+        <v>42848</v>
+      </c>
+      <c r="P37" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="R37" t="n">
+        <v>12.9</v>
       </c>
     </row>
     <row r="38">
@@ -7479,7 +7947,7 @@
         <v>5</v>
       </c>
       <c r="B38" t="n">
-        <v>402000</v>
+        <v>418000</v>
       </c>
       <c r="C38" t="n">
         <v>40</v>
@@ -7493,31 +7961,43 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>37599</v>
+        <v>37454</v>
       </c>
       <c r="G38" t="n">
         <v>20609</v>
       </c>
       <c r="H38" t="n">
-        <v>16990</v>
+        <v>16845</v>
       </c>
       <c r="I38" t="n">
-        <v>45.2</v>
+        <v>45</v>
       </c>
       <c r="J38" t="n">
-        <v>10.7</v>
+        <v>11.2</v>
       </c>
       <c r="K38" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="L38" t="n">
         <v>14</v>
       </c>
       <c r="M38" t="n">
-        <v>14.9</v>
+        <v>15.7</v>
       </c>
       <c r="N38" t="n">
-        <v>173646</v>
+        <v>155583</v>
+      </c>
+      <c r="O38" t="n">
+        <v>47369</v>
+      </c>
+      <c r="P38" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="R38" t="n">
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -7525,7 +8005,7 @@
         <v>5</v>
       </c>
       <c r="B39" t="n">
-        <v>402000</v>
+        <v>418000</v>
       </c>
       <c r="C39" t="n">
         <v>40</v>
@@ -7539,31 +8019,43 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>51903</v>
+        <v>51657</v>
       </c>
       <c r="G39" t="n">
         <v>23138</v>
       </c>
       <c r="H39" t="n">
-        <v>28765</v>
+        <v>28519</v>
       </c>
       <c r="I39" t="n">
-        <v>55.4</v>
+        <v>55.2</v>
       </c>
       <c r="J39" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="K39" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="L39" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="M39" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>385337</v>
+        <v>365844</v>
+      </c>
+      <c r="O39" t="n">
+        <v>53887</v>
+      </c>
+      <c r="P39" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R39" t="n">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -7571,7 +8063,7 @@
         <v>5</v>
       </c>
       <c r="B40" t="n">
-        <v>402000</v>
+        <v>418000</v>
       </c>
       <c r="C40" t="n">
         <v>40</v>
@@ -7585,31 +8077,43 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>31449</v>
+        <v>31303</v>
       </c>
       <c r="G40" t="n">
         <v>14458</v>
       </c>
       <c r="H40" t="n">
-        <v>16990</v>
+        <v>16845</v>
       </c>
       <c r="I40" t="n">
-        <v>54</v>
+        <v>53.8</v>
       </c>
       <c r="J40" t="n">
-        <v>12.8</v>
+        <v>13.4</v>
       </c>
       <c r="K40" t="n">
-        <v>8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="M40" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="N40" t="n">
-        <v>64933</v>
+        <v>46869</v>
+      </c>
+      <c r="O40" t="n">
+        <v>34659</v>
+      </c>
+      <c r="P40" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>16.1</v>
       </c>
     </row>
     <row r="41">
@@ -7617,7 +8121,7 @@
         <v>5</v>
       </c>
       <c r="B41" t="n">
-        <v>402000</v>
+        <v>418000</v>
       </c>
       <c r="C41" t="n">
         <v>40</v>
@@ -7631,31 +8135,43 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>44984</v>
+        <v>44738</v>
       </c>
       <c r="G41" t="n">
         <v>16219</v>
       </c>
       <c r="H41" t="n">
-        <v>28765</v>
+        <v>28519</v>
       </c>
       <c r="I41" t="n">
-        <v>63.9</v>
+        <v>63.7</v>
       </c>
       <c r="J41" t="n">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="L41" t="n">
         <v>11.7</v>
       </c>
       <c r="M41" t="n">
-        <v>12.3</v>
+        <v>13</v>
       </c>
       <c r="N41" t="n">
-        <v>263035</v>
+        <v>243541</v>
+      </c>
+      <c r="O41" t="n">
+        <v>42849</v>
+      </c>
+      <c r="P41" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="R41" t="n">
+        <v>12.9</v>
       </c>
     </row>
     <row r="42">
@@ -7663,7 +8179,7 @@
         <v>5</v>
       </c>
       <c r="B42" t="n">
-        <v>402000</v>
+        <v>418000</v>
       </c>
       <c r="C42" t="n">
         <v>50</v>
@@ -7677,31 +8193,43 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>39756</v>
+        <v>39631</v>
       </c>
       <c r="G42" t="n">
         <v>25388</v>
       </c>
       <c r="H42" t="n">
-        <v>14368</v>
+        <v>14243</v>
       </c>
       <c r="I42" t="n">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="J42" t="n">
-        <v>10.1</v>
+        <v>10.5</v>
       </c>
       <c r="K42" t="n">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="L42" t="n">
         <v>13.2</v>
       </c>
       <c r="M42" t="n">
-        <v>13.5</v>
+        <v>14.2</v>
       </c>
       <c r="N42" t="n">
-        <v>220928</v>
+        <v>203157</v>
+      </c>
+      <c r="O42" t="n">
+        <v>47366</v>
+      </c>
+      <c r="P42" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="R42" t="n">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -7709,7 +8237,7 @@
         <v>5</v>
       </c>
       <c r="B43" t="n">
-        <v>402000</v>
+        <v>418000</v>
       </c>
       <c r="C43" t="n">
         <v>50</v>
@@ -7723,31 +8251,43 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>52829</v>
+        <v>52617</v>
       </c>
       <c r="G43" t="n">
         <v>28504</v>
       </c>
       <c r="H43" t="n">
-        <v>24325</v>
+        <v>24113</v>
       </c>
       <c r="I43" t="n">
-        <v>46</v>
+        <v>45.8</v>
       </c>
       <c r="J43" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="K43" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="L43" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="M43" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="N43" t="n">
+        <v>398216</v>
+      </c>
+      <c r="O43" t="n">
+        <v>53884</v>
+      </c>
+      <c r="P43" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R43" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="N43" t="n">
-        <v>417213</v>
       </c>
     </row>
     <row r="44">
@@ -7755,7 +8295,7 @@
         <v>5</v>
       </c>
       <c r="B44" t="n">
-        <v>402000</v>
+        <v>418000</v>
       </c>
       <c r="C44" t="n">
         <v>50</v>
@@ -7769,31 +8309,43 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>32179</v>
+        <v>32054</v>
       </c>
       <c r="G44" t="n">
         <v>17811</v>
       </c>
       <c r="H44" t="n">
-        <v>14368</v>
+        <v>14243</v>
       </c>
       <c r="I44" t="n">
-        <v>44.6</v>
+        <v>44.4</v>
       </c>
       <c r="J44" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="K44" t="n">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="L44" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="M44" t="n">
-        <v>18.6</v>
+        <v>19.7</v>
       </c>
       <c r="N44" t="n">
-        <v>87004</v>
+        <v>69234</v>
+      </c>
+      <c r="O44" t="n">
+        <v>34656</v>
+      </c>
+      <c r="P44" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>16.1</v>
       </c>
     </row>
     <row r="45">
@@ -7801,7 +8353,7 @@
         <v>5</v>
       </c>
       <c r="B45" t="n">
-        <v>402000</v>
+        <v>418000</v>
       </c>
       <c r="C45" t="n">
         <v>50</v>
@@ -7815,31 +8367,43 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>44305</v>
+        <v>44094</v>
       </c>
       <c r="G45" t="n">
         <v>19980</v>
       </c>
       <c r="H45" t="n">
-        <v>24325</v>
+        <v>24113</v>
       </c>
       <c r="I45" t="n">
-        <v>54.9</v>
+        <v>54.7</v>
       </c>
       <c r="J45" t="n">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="K45" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="L45" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="M45" t="n">
-        <v>12.3</v>
+        <v>13</v>
       </c>
       <c r="N45" t="n">
-        <v>266549</v>
+        <v>247552</v>
+      </c>
+      <c r="O45" t="n">
+        <v>42846</v>
+      </c>
+      <c r="P45" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="R45" t="n">
+        <v>12.9</v>
       </c>
     </row>
     <row r="46">
@@ -7847,7 +8411,7 @@
         <v>10</v>
       </c>
       <c r="B46" t="n">
-        <v>746000</v>
+        <v>762000</v>
       </c>
       <c r="C46" t="n">
         <v>20</v>
@@ -7861,31 +8425,43 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>65916</v>
+        <v>65528</v>
       </c>
       <c r="G46" t="n">
         <v>20609</v>
       </c>
       <c r="H46" t="n">
-        <v>45307</v>
+        <v>44919</v>
       </c>
       <c r="I46" t="n">
-        <v>68.7</v>
+        <v>68.5</v>
       </c>
       <c r="J46" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="K46" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="L46" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="M46" t="n">
-        <v>17.5</v>
+        <v>18.2</v>
       </c>
       <c r="N46" t="n">
-        <v>200670</v>
+        <v>179166</v>
+      </c>
+      <c r="O46" t="n">
+        <v>78629</v>
+      </c>
+      <c r="P46" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="R46" t="n">
+        <v>12.8</v>
       </c>
     </row>
     <row r="47">
@@ -7893,7 +8469,7 @@
         <v>10</v>
       </c>
       <c r="B47" t="n">
-        <v>746000</v>
+        <v>762000</v>
       </c>
       <c r="C47" t="n">
         <v>20</v>
@@ -7907,31 +8483,43 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>99843</v>
+        <v>99186</v>
       </c>
       <c r="G47" t="n">
         <v>23138</v>
       </c>
       <c r="H47" t="n">
-        <v>76705</v>
+        <v>76048</v>
       </c>
       <c r="I47" t="n">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
       <c r="J47" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="K47" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L47" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="M47" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="N47" t="n">
+        <v>665330</v>
+      </c>
+      <c r="O47" t="n">
+        <v>101859</v>
+      </c>
+      <c r="P47" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="Q47" t="n">
         <v>7.5</v>
       </c>
-      <c r="K47" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L47" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="M47" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="N47" t="n">
-        <v>690647</v>
+      <c r="R47" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="48">
@@ -7939,7 +8527,7 @@
         <v>10</v>
       </c>
       <c r="B48" t="n">
-        <v>746000</v>
+        <v>762000</v>
       </c>
       <c r="C48" t="n">
         <v>20</v>
@@ -7953,31 +8541,43 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>59765</v>
+        <v>59377</v>
       </c>
       <c r="G48" t="n">
         <v>14458</v>
       </c>
       <c r="H48" t="n">
-        <v>45307</v>
+        <v>44919</v>
       </c>
       <c r="I48" t="n">
-        <v>75.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="K48" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="M48" t="n">
-        <v>20.8</v>
+        <v>21.7</v>
       </c>
       <c r="N48" t="n">
-        <v>91956</v>
+        <v>70453</v>
+      </c>
+      <c r="O48" t="n">
+        <v>63781</v>
+      </c>
+      <c r="P48" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="R48" t="n">
+        <v>17.6</v>
       </c>
     </row>
     <row r="49">
@@ -7985,7 +8585,7 @@
         <v>10</v>
       </c>
       <c r="B49" t="n">
-        <v>746000</v>
+        <v>762000</v>
       </c>
       <c r="C49" t="n">
         <v>20</v>
@@ -7999,35 +8599,47 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>92924</v>
+        <v>92267</v>
       </c>
       <c r="G49" t="n">
         <v>16219</v>
       </c>
       <c r="H49" t="n">
-        <v>76705</v>
+        <v>76048</v>
       </c>
       <c r="I49" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="L49" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="M49" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="N49" t="n">
-        <v>568345</v>
+        <v>543027</v>
+      </c>
+      <c r="O49" t="n">
+        <v>90141</v>
+      </c>
+      <c r="P49" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R49" t="n">
+        <v>10.7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N49"/>
+  <autoFilter ref="A1:R49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8038,7 +8650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -9262,7 +9874,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+          <t>data/raw/tns_microgen/2026-09.xlsx</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -9282,7 +9894,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -9309,7 +9921,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+          <t>data/raw/tns_microgen/2026-09.xlsx</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -9329,7 +9941,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9968,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+          <t>data/raw/tns_microgen/2026-09.xlsx</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -9376,7 +9988,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -9403,7 +10015,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+          <t>data/raw/tns_microgen/2026-09.xlsx</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -9423,7 +10035,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -9450,7 +10062,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+          <t>data/raw/tns_microgen/2026-09.xlsx</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -9470,7 +10082,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -9497,7 +10109,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+          <t>data/raw/tns_microgen/2026-09.xlsx</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9517,7 +10129,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -9544,7 +10156,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+          <t>data/raw/tns_microgen/2026-09.xlsx</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9564,7 +10176,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -9591,7 +10203,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>data/raw/tns_microgen/2026-08.xlsx</t>
+          <t>data/raw/tns_microgen/2026-09.xlsx</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9611,12 +10223,59 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>6.431</v>
+      </c>
+      <c r="C34" t="n">
+        <v>353542.222</v>
+      </c>
+      <c r="D34" t="n">
+        <v>142468.284</v>
+      </c>
+      <c r="E34" t="n">
+        <v>205201.43</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5872.508</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>data/raw/tns_microgen/2026-09.xlsx</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ПАО «ТНС энерго Кубань»</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>п. 52в Стандартов раскрытия информации (ПП РФ от 21.01.2004 № 24)</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/disclosure/raskrytie-informatsii-subektom-rynka-elektricheskoy-energii-moshchnosti/market-report-gp/informatsiya-ob-obemakh-i-srednevzveshennoy-tsene-pokupki-na-roznichnom-rynke-elektricheskoy-energii/</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K33"/>
+  <autoFilter ref="A1:K34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9627,16 +10286,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="39" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
@@ -10492,8 +11151,108 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>grid_connection</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>rub</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>21183</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ставка С1 (ТУ + проверка выполнения ТУ) 17 363,37 ₽ без НДС + НДС 22 %</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>сетевая организация (Россети Кубань)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Краснодарский край и Адыгея</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://base.garant.ru/413351706/89300effb84a59912210b23abe10a68f/</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>приказ ДГРТ от 24.12.2025 № 19/2025-э (ред. 06.05.2026), приложение; дом уже подключён — строительство сети не нужно; ставка С8 (учёт) не найдена</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>grid_connection_cap</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>rub_per_kW</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11470</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>льготная ставка за 1 кВт запрашиваемой мощности, с НДС</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>сетевая организация (Россети Кубань)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Краснодарский край и Адыгея</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://base.garant.ru/413351706/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>приказ ДГРТ № 19/2025-э, п. 1: плата за ТП микрогенерации физлица = минимум из (стандартизированные ставки; 11 470 ₽/кВт); выписка — docs/sources/2026-10-21_prikaz_dgrt_19-2025-e_tp.txt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J18"/>
+  <autoFilter ref="A1:J20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10504,7 +11263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -10514,9 +11273,11 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="33" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10557,15 +11318,25 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>grid_connection_rub</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>grid_connection_max_rub</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>method_low</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>method_base</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>method_high</t>
         </is>
@@ -10579,10 +11350,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>200000</v>
+        <v>217000</v>
       </c>
       <c r="D2" t="n">
-        <v>249000</v>
+        <v>266000</v>
       </c>
       <c r="E2" t="n">
         <v>375000</v>
@@ -10591,19 +11362,25 @@
         <v>52500</v>
       </c>
       <c r="G2" t="n">
-        <v>83100</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>88500</v>
+      </c>
+      <c r="H2" t="n">
+        <v>21183</v>
+      </c>
+      <c r="I2" t="n">
+        <v>34410</v>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>В: сумма компонентов по рознице</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>комплект Краснодара + монтаж + BOS</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Б: опубликованные цены «под ключ»</t>
         </is>
@@ -10617,10 +11394,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>275000</v>
+        <v>291000</v>
       </c>
       <c r="D3" t="n">
-        <v>402000</v>
+        <v>418000</v>
       </c>
       <c r="E3" t="n">
         <v>525000</v>
@@ -10629,19 +11406,25 @@
         <v>49200</v>
       </c>
       <c r="G3" t="n">
-        <v>80300</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>83600</v>
+      </c>
+      <c r="H3" t="n">
+        <v>21183</v>
+      </c>
+      <c r="I3" t="n">
+        <v>57350</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>В: сумма компонентов по рознице</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>комплект Краснодара + монтаж + BOS</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Б: опубликованные цены «под ключ»</t>
         </is>
@@ -10655,38 +11438,44 @@
         <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>536000</v>
+        <v>552000</v>
       </c>
       <c r="D4" t="n">
-        <v>746000</v>
+        <v>762000</v>
       </c>
       <c r="E4" t="n">
-        <v>975000</v>
+        <v>958000</v>
       </c>
       <c r="F4" t="n">
         <v>100000</v>
       </c>
       <c r="G4" t="n">
-        <v>74600</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>76200</v>
+      </c>
+      <c r="H4" t="n">
+        <v>21183</v>
+      </c>
+      <c r="I4" t="n">
+        <v>114700</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>В: сумма компонентов по рознице</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>комплект Краснодара + монтаж + BOS</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Б: опубликованные цены «под ключ» (экстраполяция от 5 кВт)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J4"/>
+  <autoFilter ref="A1:L4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/SunCount_data.xlsx
+++ b/SunCount_data.xlsx
@@ -11,28 +11,30 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="buyback_prices" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="capex_components" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="capex_estimate" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="equipment_offers" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kp_responses" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stub_energy_metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stub_energy_metrics_monthly" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tariff_ranges_2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tariffs_2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnkey_prices" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stub_payback" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="energy_metrics" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="equipment_offers" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kp_responses" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stub_energy_metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stub_energy_metrics_monthly" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tariff_ranges_2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tariffs_2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnkey_prices" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stub_payback" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'buyback_by_category'!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'buyback_prices'!$A$1:$K$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'capex_components'!$A$1:$J$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'capex_estimate'!$A$1:$L$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'equipment_offers'!$A$1:$Q$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'kp_responses'!$A$1:$Q$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'stub_energy_metrics'!$A$1:$L$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'stub_energy_metrics_monthly'!$A$1:$M$145</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'tariff_ranges_2026'!$A$1:$H$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'tariffs_2026'!$A$1:$M$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'turnkey_prices'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'stub_payback'!$A$1:$R$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'energy_metrics'!$A$1:$L$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'equipment_offers'!$A$1:$Q$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'kp_responses'!$A$1:$Q$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'stub_energy_metrics'!$A$1:$L$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'stub_energy_metrics_monthly'!$A$1:$M$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'tariff_ranges_2026'!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'tariffs_2026'!$A$1:$M$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'turnkey_prices'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'stub_payback'!$A$1:$R$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -779,6 +781,301 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="59" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>dwelling</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>range_I_max_kwh_month</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>range_II_max_kwh_month</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>accessed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>all_year</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Раздел 1, жилые дома</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>reduced_gas_rural</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>all_year</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Раздел 8, село, газовые плиты, жилые дома</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>reduced_stove</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>all_year</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1850</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Разделы 3 и 6, электроплиты без электроотопления, жилые дома</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>reduced_heating</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>heating_oct_apr</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3900</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Разделы 2,4,5,7, электроотопление, отопительный период 01.10–30.04</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>reduced_heating_stove</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>non_heating_may_sep</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1850</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Разделы 2 и 5, плиты + электроотопление, неотопительный период</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>reduced_heating_nostove</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>non_heating_may_sep</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Разделы 4 и 7, электроотопление без плит, неотопительный период</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5550,7 +5847,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5725,7 +6022,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5883,7 +6180,7 @@
         <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>19.1</v>
+        <v>20.1</v>
       </c>
       <c r="M2" t="n">
         <v>24.6</v>
@@ -5941,7 +6238,7 @@
         <v>7.3</v>
       </c>
       <c r="L3" t="n">
-        <v>12.6</v>
+        <v>13.3</v>
       </c>
       <c r="M3" t="n">
         <v>13.5</v>
@@ -5999,7 +6296,7 @@
         <v>12.2</v>
       </c>
       <c r="L4" t="n">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6059,7 +6356,7 @@
         <v>7.8</v>
       </c>
       <c r="L5" t="n">
-        <v>13.5</v>
+        <v>14.3</v>
       </c>
       <c r="M5" t="n">
         <v>15.2</v>
@@ -6117,7 +6414,7 @@
         <v>10.3</v>
       </c>
       <c r="L6" t="n">
-        <v>17.8</v>
+        <v>18.8</v>
       </c>
       <c r="M6" t="n">
         <v>20.9</v>
@@ -6175,7 +6472,7 @@
         <v>7.1</v>
       </c>
       <c r="L7" t="n">
-        <v>12.3</v>
+        <v>13</v>
       </c>
       <c r="M7" t="n">
         <v>12.7</v>
@@ -6233,7 +6530,7 @@
         <v>11.9</v>
       </c>
       <c r="L8" t="n">
-        <v>20.5</v>
+        <v>21.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -6293,7 +6590,7 @@
         <v>8</v>
       </c>
       <c r="L9" t="n">
-        <v>13.8</v>
+        <v>14.5</v>
       </c>
       <c r="M9" t="n">
         <v>15.1</v>
@@ -6351,7 +6648,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>16.7</v>
+        <v>17.6</v>
       </c>
       <c r="M10" t="n">
         <v>18.2</v>
@@ -6409,10 +6706,10 @@
         <v>7</v>
       </c>
       <c r="L11" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M11" t="n">
         <v>12.1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>10.5</v>
       </c>
       <c r="N11" t="n">
         <v>190495</v>
@@ -6467,7 +6764,7 @@
         <v>11.6</v>
       </c>
       <c r="L12" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -6527,7 +6824,7 @@
         <v>8.1</v>
       </c>
       <c r="L13" t="n">
-        <v>14</v>
+        <v>14.8</v>
       </c>
       <c r="M13" t="n">
         <v>15</v>
@@ -6585,7 +6882,7 @@
         <v>9.1</v>
       </c>
       <c r="L14" t="n">
-        <v>15.7</v>
+        <v>16.6</v>
       </c>
       <c r="M14" t="n">
         <v>16.2</v>
@@ -6643,7 +6940,7 @@
         <v>6.9</v>
       </c>
       <c r="L15" t="n">
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
       <c r="M15" t="n">
         <v>10</v>
@@ -6701,7 +6998,7 @@
         <v>11.3</v>
       </c>
       <c r="L16" t="n">
-        <v>19.5</v>
+        <v>20.6</v>
       </c>
       <c r="M16" t="n">
         <v>23.2</v>
@@ -6759,7 +7056,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="M17" t="n">
         <v>14.9</v>
@@ -6817,7 +7114,7 @@
         <v>8.6</v>
       </c>
       <c r="L18" t="n">
-        <v>14.8</v>
+        <v>15.7</v>
       </c>
       <c r="M18" t="n">
         <v>14.6</v>
@@ -6875,7 +7172,7 @@
         <v>6.7</v>
       </c>
       <c r="L19" t="n">
-        <v>11.6</v>
+        <v>12.3</v>
       </c>
       <c r="M19" t="n">
         <v>9.5</v>
@@ -6933,7 +7230,7 @@
         <v>11</v>
       </c>
       <c r="L20" t="n">
-        <v>19</v>
+        <v>20.1</v>
       </c>
       <c r="M20" t="n">
         <v>21.5</v>
@@ -6991,7 +7288,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>14.4</v>
+        <v>15.2</v>
       </c>
       <c r="M21" t="n">
         <v>14.8</v>
@@ -7049,7 +7346,7 @@
         <v>8.1</v>
       </c>
       <c r="L22" t="n">
-        <v>14</v>
+        <v>14.8</v>
       </c>
       <c r="M22" t="n">
         <v>13.3</v>
@@ -7107,7 +7404,7 @@
         <v>6.6</v>
       </c>
       <c r="L23" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="M23" t="n">
         <v>9.1</v>
@@ -7165,7 +7462,7 @@
         <v>10.7</v>
       </c>
       <c r="L24" t="n">
-        <v>18.5</v>
+        <v>19.6</v>
       </c>
       <c r="M24" t="n">
         <v>20.1</v>
@@ -7223,7 +7520,7 @@
         <v>8.5</v>
       </c>
       <c r="L25" t="n">
-        <v>14.7</v>
+        <v>15.5</v>
       </c>
       <c r="M25" t="n">
         <v>14.7</v>
@@ -7281,10 +7578,10 @@
         <v>7.7</v>
       </c>
       <c r="L26" t="n">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="M26" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
       </c>
       <c r="N26" t="n">
         <v>186114</v>
@@ -7339,7 +7636,7 @@
         <v>6.5</v>
       </c>
       <c r="L27" t="n">
-        <v>11.2</v>
+        <v>11.8</v>
       </c>
       <c r="M27" t="n">
         <v>8.800000000000001</v>
@@ -7397,7 +7694,7 @@
         <v>10.5</v>
       </c>
       <c r="L28" t="n">
-        <v>18.1</v>
+        <v>19.1</v>
       </c>
       <c r="M28" t="n">
         <v>18.9</v>
@@ -7455,7 +7752,7 @@
         <v>8.6</v>
       </c>
       <c r="L29" t="n">
-        <v>14.9</v>
+        <v>15.7</v>
       </c>
       <c r="M29" t="n">
         <v>14.6</v>
@@ -7513,7 +7810,7 @@
         <v>8.9</v>
       </c>
       <c r="L30" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="M30" t="n">
         <v>20.7</v>
@@ -7571,7 +7868,7 @@
         <v>5.9</v>
       </c>
       <c r="L31" t="n">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="M31" t="n">
         <v>10.8</v>
@@ -7629,7 +7926,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>17.7</v>
+        <v>18.4</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -7689,7 +7986,7 @@
         <v>6.3</v>
       </c>
       <c r="L33" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="M33" t="n">
         <v>13.2</v>
@@ -7747,7 +8044,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="M34" t="n">
         <v>17.9</v>
@@ -7805,7 +8102,7 @@
         <v>5.7</v>
       </c>
       <c r="L35" t="n">
-        <v>10.4</v>
+        <v>10.8</v>
       </c>
       <c r="M35" t="n">
         <v>10.2</v>
@@ -7863,7 +8160,7 @@
         <v>9.5</v>
       </c>
       <c r="L36" t="n">
-        <v>17.2</v>
+        <v>17.9</v>
       </c>
       <c r="M36" t="n">
         <v>23</v>
@@ -7921,7 +8218,7 @@
         <v>6.4</v>
       </c>
       <c r="L37" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="M37" t="n">
         <v>13.1</v>
@@ -7979,7 +8276,7 @@
         <v>7.8</v>
       </c>
       <c r="L38" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="M38" t="n">
         <v>15.7</v>
@@ -8037,7 +8334,7 @@
         <v>5.6</v>
       </c>
       <c r="L39" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="M39" t="n">
         <v>9.699999999999999</v>
@@ -8095,7 +8392,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="M40" t="n">
         <v>21.2</v>
@@ -8153,7 +8450,7 @@
         <v>6.5</v>
       </c>
       <c r="L41" t="n">
-        <v>11.7</v>
+        <v>12.2</v>
       </c>
       <c r="M41" t="n">
         <v>13</v>
@@ -8211,7 +8508,7 @@
         <v>7.3</v>
       </c>
       <c r="L42" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="M42" t="n">
         <v>14.2</v>
@@ -8269,7 +8566,7 @@
         <v>5.5</v>
       </c>
       <c r="L43" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="M43" t="n">
         <v>9.300000000000001</v>
@@ -8327,7 +8624,7 @@
         <v>9.1</v>
       </c>
       <c r="L44" t="n">
-        <v>16.4</v>
+        <v>17</v>
       </c>
       <c r="M44" t="n">
         <v>19.7</v>
@@ -8385,7 +8682,7 @@
         <v>6.6</v>
       </c>
       <c r="L45" t="n">
-        <v>11.9</v>
+        <v>12.4</v>
       </c>
       <c r="M45" t="n">
         <v>13</v>
@@ -8443,7 +8740,7 @@
         <v>8.4</v>
       </c>
       <c r="L46" t="n">
-        <v>14.6</v>
+        <v>15.2</v>
       </c>
       <c r="M46" t="n">
         <v>18.2</v>
@@ -8501,7 +8798,7 @@
         <v>5.6</v>
       </c>
       <c r="L47" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="M47" t="n">
         <v>9.6</v>
@@ -8559,7 +8856,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>16.1</v>
+        <v>16.8</v>
       </c>
       <c r="M48" t="n">
         <v>21.7</v>
@@ -8617,7 +8914,7 @@
         <v>6</v>
       </c>
       <c r="L49" t="n">
-        <v>10.4</v>
+        <v>10.8</v>
       </c>
       <c r="M49" t="n">
         <v>10.7</v>
@@ -11356,13 +11653,13 @@
         <v>266000</v>
       </c>
       <c r="E2" t="n">
-        <v>375000</v>
+        <v>396000</v>
       </c>
       <c r="F2" t="n">
         <v>52500</v>
       </c>
       <c r="G2" t="n">
-        <v>88500</v>
+        <v>88700</v>
       </c>
       <c r="H2" t="n">
         <v>21183</v>
@@ -11400,7 +11697,7 @@
         <v>418000</v>
       </c>
       <c r="E3" t="n">
-        <v>525000</v>
+        <v>546000</v>
       </c>
       <c r="F3" t="n">
         <v>49200</v>
@@ -11444,7 +11741,7 @@
         <v>762000</v>
       </c>
       <c r="E4" t="n">
-        <v>958000</v>
+        <v>998000</v>
       </c>
       <c r="F4" t="n">
         <v>100000</v>
@@ -11481,6 +11778,1105 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>profile_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pv_kw</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>gen_kwh</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>load_kwh</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>self_kwh</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>export_kwh</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>import_kwh</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>import_day_kwh</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>import_night_kwh</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>self_share</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>day_absent</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>krasnodar</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3665.53731</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3229.74061</v>
+      </c>
+      <c r="F2" t="n">
+        <v>671.302785</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2994.234525</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2558.437825</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2104.1616</v>
+      </c>
+      <c r="J2" t="n">
+        <v>454.276225</v>
+      </c>
+      <c r="K2" t="n">
+        <v>18.313899</v>
+      </c>
+      <c r="L2" t="n">
+        <v>20.785037</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>day_absent</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>krasnodar</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6109.22885</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3229.74061</v>
+      </c>
+      <c r="F3" t="n">
+        <v>735.476477</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5373.752373</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2494.264133</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2044.809528</v>
+      </c>
+      <c r="J3" t="n">
+        <v>449.454605</v>
+      </c>
+      <c r="K3" t="n">
+        <v>12.038778</v>
+      </c>
+      <c r="L3" t="n">
+        <v>22.771998</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>day_absent</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>krasnodar</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12218.4577</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3229.74061</v>
+      </c>
+      <c r="F4" t="n">
+        <v>813.440908</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11405.016792</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2416.299702</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1978.695844</v>
+      </c>
+      <c r="J4" t="n">
+        <v>437.603858</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.657476</v>
+      </c>
+      <c r="L4" t="n">
+        <v>25.185952</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>home_all_day</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>krasnodar</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3665.53731</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3793.165857</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1083.59232</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2581.94499</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2709.573537</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2255.451345</v>
+      </c>
+      <c r="J5" t="n">
+        <v>454.122192</v>
+      </c>
+      <c r="K5" t="n">
+        <v>29.561623</v>
+      </c>
+      <c r="L5" t="n">
+        <v>28.566964</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>home_all_day</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>krasnodar</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6109.22885</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3793.165857</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1184.12774</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4925.10111</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2609.038117</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2158.874739</v>
+      </c>
+      <c r="J6" t="n">
+        <v>450.163378</v>
+      </c>
+      <c r="K6" t="n">
+        <v>19.382606</v>
+      </c>
+      <c r="L6" t="n">
+        <v>31.2174</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>home_all_day</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>krasnodar</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>12218.4577</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3793.165857</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1296.672392</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10921.785308</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2496.493465</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2055.711805</v>
+      </c>
+      <c r="J7" t="n">
+        <v>440.78166</v>
+      </c>
+      <c r="K7" t="n">
+        <v>10.612406</v>
+      </c>
+      <c r="L7" t="n">
+        <v>34.184437</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ac</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>krasnodar</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3665.53731</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3915.34747</v>
+      </c>
+      <c r="F8" t="n">
+        <v>821.860528</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2843.676782</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3093.486942</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2646.958604</v>
+      </c>
+      <c r="J8" t="n">
+        <v>446.528338</v>
+      </c>
+      <c r="K8" t="n">
+        <v>22.421284</v>
+      </c>
+      <c r="L8" t="n">
+        <v>20.990743</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ac</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>krasnodar</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6109.22885</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3915.34747</v>
+      </c>
+      <c r="F9" t="n">
+        <v>939.759819</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5169.469031</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2975.587651</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2533.287641</v>
+      </c>
+      <c r="J9" t="n">
+        <v>442.30001</v>
+      </c>
+      <c r="K9" t="n">
+        <v>15.382626</v>
+      </c>
+      <c r="L9" t="n">
+        <v>24.001952</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ac</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>krasnodar</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>12218.4577</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3915.34747</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1060.115616</v>
+      </c>
+      <c r="G10" t="n">
+        <v>11158.342084</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2855.231854</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2422.98123</v>
+      </c>
+      <c r="J10" t="n">
+        <v>432.250624</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.676346000000001</v>
+      </c>
+      <c r="L10" t="n">
+        <v>27.075901</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>el_heating</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>krasnodar</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3665.53731</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11519.952947</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1507.104961</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2158.432349</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10012.847986</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6896.443753</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3116.404233</v>
+      </c>
+      <c r="K11" t="n">
+        <v>41.115526</v>
+      </c>
+      <c r="L11" t="n">
+        <v>13.082562</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>el_heating</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>krasnodar</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6109.22885</v>
+      </c>
+      <c r="E12" t="n">
+        <v>11519.952947</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1956.401742</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4152.827108</v>
+      </c>
+      <c r="H12" t="n">
+        <v>9563.551205</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6451.512995</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3112.03821</v>
+      </c>
+      <c r="K12" t="n">
+        <v>32.02371</v>
+      </c>
+      <c r="L12" t="n">
+        <v>16.982723</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>el_heating</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>krasnodar</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12218.4577</v>
+      </c>
+      <c r="E13" t="n">
+        <v>11519.952947</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2485.350967</v>
+      </c>
+      <c r="G13" t="n">
+        <v>9733.106733000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>9034.601979999999</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5933.149587</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3101.452393</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20.340955</v>
+      </c>
+      <c r="L13" t="n">
+        <v>21.574315</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>day_absent</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>maykop</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3718.35153</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3229.112294</v>
+      </c>
+      <c r="F14" t="n">
+        <v>654.220475</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3064.131055</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2574.891819</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2123.873513</v>
+      </c>
+      <c r="J14" t="n">
+        <v>451.018306</v>
+      </c>
+      <c r="K14" t="n">
+        <v>17.594369</v>
+      </c>
+      <c r="L14" t="n">
+        <v>20.260072</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>day_absent</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>maykop</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6197.25255</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3229.112294</v>
+      </c>
+      <c r="F15" t="n">
+        <v>718.262189</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5478.990361</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2510.850105</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2063.954051</v>
+      </c>
+      <c r="J15" t="n">
+        <v>446.896054</v>
+      </c>
+      <c r="K15" t="n">
+        <v>11.59001</v>
+      </c>
+      <c r="L15" t="n">
+        <v>22.243333</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>day_absent</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>maykop</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="n">
+        <v>12394.5051</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3229.112294</v>
+      </c>
+      <c r="F16" t="n">
+        <v>794.78334</v>
+      </c>
+      <c r="G16" t="n">
+        <v>11599.72176</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2434.328954</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1997.239116</v>
+      </c>
+      <c r="J16" t="n">
+        <v>437.089838</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.412385</v>
+      </c>
+      <c r="L16" t="n">
+        <v>24.61306</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>home_all_day</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>maykop</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3718.35153</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3790.02704</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1066.137567</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2652.213963</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2723.889473</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2258.86158</v>
+      </c>
+      <c r="J17" t="n">
+        <v>465.027893</v>
+      </c>
+      <c r="K17" t="n">
+        <v>28.672318</v>
+      </c>
+      <c r="L17" t="n">
+        <v>28.130078</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>home_all_day</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>maykop</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6197.25255</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3790.02704</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1161.32189</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5035.93066</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2628.70515</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2167.995785</v>
+      </c>
+      <c r="J18" t="n">
+        <v>460.709365</v>
+      </c>
+      <c r="K18" t="n">
+        <v>18.739302</v>
+      </c>
+      <c r="L18" t="n">
+        <v>30.64152</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>home_all_day</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>maykop</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
+        <v>12394.5051</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3790.02704</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1267.179665</v>
+      </c>
+      <c r="G19" t="n">
+        <v>11127.325435</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2522.847375</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2072.426288</v>
+      </c>
+      <c r="J19" t="n">
+        <v>450.421087</v>
+      </c>
+      <c r="K19" t="n">
+        <v>10.223721</v>
+      </c>
+      <c r="L19" t="n">
+        <v>33.434581</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ac</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>maykop</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3718.35153</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3860.328306</v>
+      </c>
+      <c r="F20" t="n">
+        <v>795.405002</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2922.946528</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3064.923304</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2623.660487</v>
+      </c>
+      <c r="J20" t="n">
+        <v>441.262817</v>
+      </c>
+      <c r="K20" t="n">
+        <v>21.391334</v>
+      </c>
+      <c r="L20" t="n">
+        <v>20.604595</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ac</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>maykop</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6197.25255</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3860.328306</v>
+      </c>
+      <c r="F21" t="n">
+        <v>893.50182</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5303.75073</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2966.826486</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2529.632207</v>
+      </c>
+      <c r="J21" t="n">
+        <v>437.194279</v>
+      </c>
+      <c r="K21" t="n">
+        <v>14.417709</v>
+      </c>
+      <c r="L21" t="n">
+        <v>23.145747</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ac</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>maykop</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>12394.5051</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3860.328306</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1007.027088</v>
+      </c>
+      <c r="G22" t="n">
+        <v>11387.478012</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2853.301218</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2425.77024</v>
+      </c>
+      <c r="J22" t="n">
+        <v>427.530978</v>
+      </c>
+      <c r="K22" t="n">
+        <v>8.124787</v>
+      </c>
+      <c r="L22" t="n">
+        <v>26.086566</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>el_heating</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>maykop</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3718.35153</v>
+      </c>
+      <c r="E23" t="n">
+        <v>11912.105283</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1600.921258</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2117.430272</v>
+      </c>
+      <c r="H23" t="n">
+        <v>10311.184025</v>
+      </c>
+      <c r="I23" t="n">
+        <v>7084.024536</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3227.159489</v>
+      </c>
+      <c r="K23" t="n">
+        <v>43.054597</v>
+      </c>
+      <c r="L23" t="n">
+        <v>13.439449</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>el_heating</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>maykop</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>6197.25255</v>
+      </c>
+      <c r="E24" t="n">
+        <v>11912.105283</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2089.045421</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4108.207129</v>
+      </c>
+      <c r="H24" t="n">
+        <v>9823.059862</v>
+      </c>
+      <c r="I24" t="n">
+        <v>6599.3123</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3223.747562</v>
+      </c>
+      <c r="K24" t="n">
+        <v>33.709219</v>
+      </c>
+      <c r="L24" t="n">
+        <v>17.537164</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>el_heating</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>maykop</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" t="n">
+        <v>12394.5051</v>
+      </c>
+      <c r="E25" t="n">
+        <v>11912.105283</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2627.708493</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9766.796607</v>
+      </c>
+      <c r="H25" t="n">
+        <v>9284.396790000001</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6068.786529</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3215.610261</v>
+      </c>
+      <c r="K25" t="n">
+        <v>21.200592</v>
+      </c>
+      <c r="L25" t="n">
+        <v>22.059144</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L25"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12176,7 +13572,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12468,7 +13864,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13063,7 +14459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19638,299 +21034,4 @@
   <autoFilter ref="A1:M145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="59" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>dwelling</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>season</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>range_I_max_kwh_month</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>range_II_max_kwh_month</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>source_url</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>accessed</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>all_year</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1700</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Раздел 1, жилые дома</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>reduced_gas_rural</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>all_year</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1100</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1700</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Раздел 8, село, газовые плиты, жилые дома</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>reduced_stove</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>all_year</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Разделы 3 и 6, электроплиты без электроотопления, жилые дома</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>reduced_heating</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>heating_oct_apr</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3900</v>
-      </c>
-      <c r="E5" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Разделы 2,4,5,7, электроотопление, отопительный период 01.10–30.04</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>reduced_heating_stove</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>non_heating_may_sep</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Разделы 2 и 5, плиты + электроотопление, неотопительный период</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>reduced_heating_nostove</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>non_heating_may_sep</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1100</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1700</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Разделы 4 и 7, электроотопление без плит, неотопительный период</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://kuban.tns-e.ru/calculations/tariffs/tariff-table/</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H7"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>